--- a/research/traditional_assets/database/data/norway/norway_retail_general.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_retail_general.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08739319017856016</v>
+        <v>0.08723602516016733</v>
       </c>
       <c r="C2">
-        <v>1441.919400071108</v>
+        <v>1429.620890961538</v>
       </c>
       <c r="D2">
-        <v>1432.949400071108</v>
+        <v>1436.047890961538</v>
       </c>
       <c r="E2">
-        <v>-492.5</v>
+        <v>-477.103</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15.397</v>
       </c>
       <c r="G2">
         <v>8.970000000000001</v>
@@ -1451,28 +1451,28 @@
         <v>41</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7744691</v>
       </c>
       <c r="N2">
-        <v>41</v>
+        <v>40.2255309</v>
       </c>
       <c r="O2">
-        <v>9.02</v>
+        <v>8.849616798000001</v>
       </c>
       <c r="P2">
-        <v>31.98</v>
+        <v>31.375914102</v>
       </c>
       <c r="Q2">
-        <v>110.98</v>
+        <v>110.375914102</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08739319017856016</v>
+        <v>0.08772089410117911</v>
       </c>
       <c r="T2">
-        <v>0.9605817593200962</v>
+        <v>0.968149979242012</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>52.93949106555704</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08723602516016733</v>
+        <v>0.08707886014177449</v>
       </c>
       <c r="C3">
-        <v>1429.620890961538</v>
+        <v>1417.335810728694</v>
       </c>
       <c r="D3">
-        <v>1436.047890961538</v>
+        <v>1439.159810728694</v>
       </c>
       <c r="E3">
-        <v>-477.103</v>
+        <v>-461.706</v>
       </c>
       <c r="F3">
-        <v>15.397</v>
+        <v>30.794</v>
       </c>
       <c r="G3">
         <v>8.970000000000001</v>
@@ -1533,28 +1533,28 @@
         <v>41</v>
       </c>
       <c r="M3">
-        <v>0.7744691</v>
+        <v>1.5489382</v>
       </c>
       <c r="N3">
-        <v>40.2255309</v>
+        <v>39.4510618</v>
       </c>
       <c r="O3">
-        <v>8.849616798000001</v>
+        <v>8.679233596</v>
       </c>
       <c r="P3">
-        <v>31.375914102</v>
+        <v>30.771828204</v>
       </c>
       <c r="Q3">
-        <v>110.375914102</v>
+        <v>109.771828204</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08772089410117911</v>
+        <v>0.08805528585895357</v>
       </c>
       <c r="T3">
-        <v>0.968149979242012</v>
+        <v>0.9758726526317222</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>52.93949106555704</v>
+        <v>26.46974553277852</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08707886014177449</v>
+        <v>0.08692169512338167</v>
       </c>
       <c r="C4">
-        <v>1417.335810728694</v>
+        <v>1405.064246863408</v>
       </c>
       <c r="D4">
-        <v>1439.159810728694</v>
+        <v>1442.285246863408</v>
       </c>
       <c r="E4">
-        <v>-461.706</v>
+        <v>-446.309</v>
       </c>
       <c r="F4">
-        <v>30.794</v>
+        <v>46.191</v>
       </c>
       <c r="G4">
         <v>8.970000000000001</v>
@@ -1615,28 +1615,28 @@
         <v>41</v>
       </c>
       <c r="M4">
-        <v>1.5489382</v>
+        <v>2.3234073</v>
       </c>
       <c r="N4">
-        <v>39.4510618</v>
+        <v>38.6765927</v>
       </c>
       <c r="O4">
-        <v>8.679233596</v>
+        <v>8.508850394</v>
       </c>
       <c r="P4">
-        <v>30.771828204</v>
+        <v>30.167742306</v>
       </c>
       <c r="Q4">
-        <v>109.771828204</v>
+        <v>109.167742306</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08805528585895357</v>
+        <v>0.08839657229214605</v>
       </c>
       <c r="T4">
-        <v>0.9758726526317222</v>
+        <v>0.9837545564006016</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>26.46974553277852</v>
+        <v>17.64649702185235</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08692169512338167</v>
+        <v>0.08676453010498883</v>
       </c>
       <c r="C5">
-        <v>1405.064246863408</v>
+        <v>1392.806287618185</v>
       </c>
       <c r="D5">
-        <v>1442.285246863408</v>
+        <v>1445.424287618185</v>
       </c>
       <c r="E5">
-        <v>-446.309</v>
+        <v>-430.912</v>
       </c>
       <c r="F5">
-        <v>46.191</v>
+        <v>61.588</v>
       </c>
       <c r="G5">
         <v>8.970000000000001</v>
@@ -1697,28 +1697,28 @@
         <v>41</v>
       </c>
       <c r="M5">
-        <v>2.3234073</v>
+        <v>3.0978764</v>
       </c>
       <c r="N5">
-        <v>38.6765927</v>
+        <v>37.9021236</v>
       </c>
       <c r="O5">
-        <v>8.508850394</v>
+        <v>8.338467192000001</v>
       </c>
       <c r="P5">
-        <v>30.167742306</v>
+        <v>29.563656408</v>
       </c>
       <c r="Q5">
-        <v>109.167742306</v>
+        <v>108.563656408</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08839657229214605</v>
+        <v>0.08874496885936337</v>
       </c>
       <c r="T5">
-        <v>0.9837545564006016</v>
+        <v>0.9918006664979993</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>17.64649702185235</v>
+        <v>13.23487276638926</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08676453010498883</v>
+        <v>0.08666586508659602</v>
       </c>
       <c r="C6">
-        <v>1392.806287618185</v>
+        <v>1379.386904890301</v>
       </c>
       <c r="D6">
-        <v>1445.424287618185</v>
+        <v>1447.401904890301</v>
       </c>
       <c r="E6">
-        <v>-430.912</v>
+        <v>-415.515</v>
       </c>
       <c r="F6">
-        <v>61.588</v>
+        <v>76.98500000000001</v>
       </c>
       <c r="G6">
         <v>8.970000000000001</v>
@@ -1779,45 +1779,45 @@
         <v>41</v>
       </c>
       <c r="M6">
-        <v>3.0978764</v>
+        <v>3.987823000000001</v>
       </c>
       <c r="N6">
-        <v>37.9021236</v>
+        <v>37.012177</v>
       </c>
       <c r="O6">
-        <v>8.338467192000001</v>
+        <v>8.14267894</v>
       </c>
       <c r="P6">
-        <v>29.563656408</v>
+        <v>28.86949806</v>
       </c>
       <c r="Q6">
-        <v>108.563656408</v>
+        <v>107.86949806</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08874496885936337</v>
+        <v>0.0891007000911537</v>
       </c>
       <c r="T6">
-        <v>0.9918006664979993</v>
+        <v>1.000016168386921</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>13.23487276638926</v>
+        <v>10.28129884400586</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08666586508659602</v>
+        <v>0.08659996006820316</v>
       </c>
       <c r="C7">
-        <v>1379.386904890301</v>
+        <v>1365.313906183147</v>
       </c>
       <c r="D7">
-        <v>1447.401904890301</v>
+        <v>1448.725906183147</v>
       </c>
       <c r="E7">
-        <v>-415.515</v>
+        <v>-400.118</v>
       </c>
       <c r="F7">
-        <v>76.98500000000001</v>
+        <v>92.38200000000001</v>
       </c>
       <c r="G7">
         <v>8.970000000000001</v>
@@ -1861,45 +1861,45 @@
         <v>41</v>
       </c>
       <c r="M7">
-        <v>3.987823000000001</v>
+        <v>4.942437</v>
       </c>
       <c r="N7">
-        <v>37.012177</v>
+        <v>36.057563</v>
       </c>
       <c r="O7">
-        <v>8.14267894</v>
+        <v>7.932663860000001</v>
       </c>
       <c r="P7">
-        <v>28.86949806</v>
+        <v>28.12489914</v>
       </c>
       <c r="Q7">
-        <v>107.86949806</v>
+        <v>107.12489914</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0891007000911537</v>
+        <v>0.08946400007255656</v>
       </c>
       <c r="T7">
-        <v>1.000016168386921</v>
+        <v>1.008406468188373</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>10.28129884400586</v>
+        <v>8.295502805599748</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08659996006820316</v>
+        <v>0.08651143504981033</v>
       </c>
       <c r="C8">
-        <v>1365.313906183147</v>
+        <v>1351.699149449643</v>
       </c>
       <c r="D8">
-        <v>1448.725906183147</v>
+        <v>1450.508149449643</v>
       </c>
       <c r="E8">
-        <v>-400.118</v>
+        <v>-384.721</v>
       </c>
       <c r="F8">
-        <v>92.38200000000001</v>
+        <v>107.779</v>
       </c>
       <c r="G8">
         <v>8.970000000000001</v>
@@ -1943,45 +1943,45 @@
         <v>41</v>
       </c>
       <c r="M8">
-        <v>4.942437</v>
+        <v>5.8523997</v>
       </c>
       <c r="N8">
-        <v>36.057563</v>
+        <v>35.1476003</v>
       </c>
       <c r="O8">
-        <v>7.932663860000001</v>
+        <v>7.732472066000001</v>
       </c>
       <c r="P8">
-        <v>28.12489914</v>
+        <v>27.415128234</v>
       </c>
       <c r="Q8">
-        <v>107.12489914</v>
+        <v>106.415128234</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08946400007255656</v>
+        <v>0.0898351129567853</v>
       </c>
       <c r="T8">
-        <v>1.008406468188373</v>
+        <v>1.016977204544695</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>8.295502805599748</v>
+        <v>7.005673245455193</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08651143504981033</v>
+        <v>0.08638547003141751</v>
       </c>
       <c r="C9">
-        <v>1351.699149449643</v>
+        <v>1338.845731557507</v>
       </c>
       <c r="D9">
-        <v>1450.508149449643</v>
+        <v>1453.051731557507</v>
       </c>
       <c r="E9">
-        <v>-384.721</v>
+        <v>-369.324</v>
       </c>
       <c r="F9">
-        <v>107.779</v>
+        <v>123.176</v>
       </c>
       <c r="G9">
         <v>8.970000000000001</v>
@@ -2025,28 +2025,28 @@
         <v>41</v>
       </c>
       <c r="M9">
-        <v>5.8523997</v>
+        <v>6.6884568</v>
       </c>
       <c r="N9">
-        <v>35.1476003</v>
+        <v>34.3115432</v>
       </c>
       <c r="O9">
-        <v>7.732472066000001</v>
+        <v>7.548539504000001</v>
       </c>
       <c r="P9">
-        <v>27.415128234</v>
+        <v>26.763003696</v>
       </c>
       <c r="Q9">
-        <v>106.415128234</v>
+        <v>105.763003696</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08983511295678531</v>
+        <v>0.09021429351241034</v>
       </c>
       <c r="T9">
-        <v>1.016977204544695</v>
+        <v>1.02573426125659</v>
       </c>
       <c r="U9">
         <v>0.0543</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>7.005673245455193</v>
+        <v>6.129964089773295</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08638547003141751</v>
+        <v>0.08632970501302469</v>
       </c>
       <c r="C10">
-        <v>1338.845731557507</v>
+        <v>1324.577632510854</v>
       </c>
       <c r="D10">
-        <v>1453.051731557507</v>
+        <v>1454.180632510854</v>
       </c>
       <c r="E10">
-        <v>-369.324</v>
+        <v>-353.927</v>
       </c>
       <c r="F10">
-        <v>123.176</v>
+        <v>138.573</v>
       </c>
       <c r="G10">
         <v>8.970000000000001</v>
@@ -2107,45 +2107,45 @@
         <v>41</v>
       </c>
       <c r="M10">
-        <v>6.6884568</v>
+        <v>7.663086900000001</v>
       </c>
       <c r="N10">
-        <v>34.3115432</v>
+        <v>33.3369131</v>
       </c>
       <c r="O10">
-        <v>7.548539504000001</v>
+        <v>7.334120882</v>
       </c>
       <c r="P10">
-        <v>26.763003696</v>
+        <v>26.002792218</v>
       </c>
       <c r="Q10">
-        <v>105.763003696</v>
+        <v>105.002792218</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09021429351241034</v>
+        <v>0.09060180770662052</v>
       </c>
       <c r="T10">
-        <v>1.02573426125659</v>
+        <v>1.034683780753361</v>
       </c>
       <c r="U10">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>6.129964089773295</v>
+        <v>5.350324292942573</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08632970501302469</v>
+        <v>0.08621153999463183</v>
       </c>
       <c r="C11">
-        <v>1324.577632510854</v>
+        <v>1311.578558381495</v>
       </c>
       <c r="D11">
-        <v>1454.180632510854</v>
+        <v>1456.578558381495</v>
       </c>
       <c r="E11">
-        <v>-353.927</v>
+        <v>-338.53</v>
       </c>
       <c r="F11">
-        <v>138.573</v>
+        <v>153.97</v>
       </c>
       <c r="G11">
         <v>8.970000000000001</v>
@@ -2189,28 +2189,28 @@
         <v>41</v>
       </c>
       <c r="M11">
-        <v>7.663086900000001</v>
+        <v>8.514540999999999</v>
       </c>
       <c r="N11">
-        <v>33.3369131</v>
+        <v>32.485459</v>
       </c>
       <c r="O11">
-        <v>7.334120882</v>
+        <v>7.14680098</v>
       </c>
       <c r="P11">
-        <v>26.002792218</v>
+        <v>25.33865802</v>
       </c>
       <c r="Q11">
-        <v>105.002792218</v>
+        <v>104.33865802</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09060180770662052</v>
+        <v>0.0909979333273687</v>
       </c>
       <c r="T11">
-        <v>1.034683780753361</v>
+        <v>1.043832178461171</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.350324292942573</v>
+        <v>4.815291863648317</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08621153999463183</v>
+        <v>0.08630787497623901</v>
       </c>
       <c r="C12">
-        <v>1311.578558381495</v>
+        <v>1294.226035285367</v>
       </c>
       <c r="D12">
-        <v>1456.578558381495</v>
+        <v>1454.623035285367</v>
       </c>
       <c r="E12">
-        <v>-338.53</v>
+        <v>-323.133</v>
       </c>
       <c r="F12">
-        <v>153.97</v>
+        <v>169.367</v>
       </c>
       <c r="G12">
         <v>8.970000000000001</v>
@@ -2271,45 +2271,45 @@
         <v>41</v>
       </c>
       <c r="M12">
-        <v>8.514541000000001</v>
+        <v>9.789412600000002</v>
       </c>
       <c r="N12">
-        <v>32.485459</v>
+        <v>31.2105874</v>
       </c>
       <c r="O12">
-        <v>7.14680098</v>
+        <v>6.866329228</v>
       </c>
       <c r="P12">
-        <v>25.33865802</v>
+        <v>24.344258172</v>
       </c>
       <c r="Q12">
-        <v>104.33865802</v>
+        <v>103.344258172</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0909979333273687</v>
+        <v>0.09140296064745956</v>
       </c>
       <c r="T12">
-        <v>1.043832178461171</v>
+        <v>1.053186158139944</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.815291863648316</v>
+        <v>4.188198176466685</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08630787497623901</v>
+        <v>0.08653680995784618</v>
       </c>
       <c r="C13">
-        <v>1294.226035285367</v>
+        <v>1274.202837123298</v>
       </c>
       <c r="D13">
-        <v>1454.623035285367</v>
+        <v>1449.996837123298</v>
       </c>
       <c r="E13">
-        <v>-323.133</v>
+        <v>-307.736</v>
       </c>
       <c r="F13">
-        <v>169.367</v>
+        <v>184.764</v>
       </c>
       <c r="G13">
         <v>8.970000000000001</v>
@@ -2353,45 +2353,45 @@
         <v>41</v>
       </c>
       <c r="M13">
-        <v>9.789412600000002</v>
+        <v>11.3260332</v>
       </c>
       <c r="N13">
-        <v>31.2105874</v>
+        <v>29.6739668</v>
       </c>
       <c r="O13">
-        <v>6.866329228</v>
+        <v>6.528272696</v>
       </c>
       <c r="P13">
-        <v>24.344258172</v>
+        <v>23.145694104</v>
       </c>
       <c r="Q13">
-        <v>103.344258172</v>
+        <v>102.145694104</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09140296064745956</v>
+        <v>0.09181719313391612</v>
       </c>
       <c r="T13">
-        <v>1.053186158139944</v>
+        <v>1.062752728265961</v>
       </c>
       <c r="U13">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>4.188198176466685</v>
+        <v>3.619978793634473</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08653680995784618</v>
+        <v>0.08674936493945334</v>
       </c>
       <c r="C14">
-        <v>1274.202837123298</v>
+        <v>1254.53690289769</v>
       </c>
       <c r="D14">
-        <v>1449.996837123298</v>
+        <v>1445.72790289769</v>
       </c>
       <c r="E14">
-        <v>-307.736</v>
+        <v>-292.339</v>
       </c>
       <c r="F14">
-        <v>184.764</v>
+        <v>200.161</v>
       </c>
       <c r="G14">
         <v>8.970000000000001</v>
@@ -2435,45 +2435,45 @@
         <v>41</v>
       </c>
       <c r="M14">
-        <v>11.3260332</v>
+        <v>12.8303201</v>
       </c>
       <c r="N14">
-        <v>29.6739668</v>
+        <v>28.1696799</v>
       </c>
       <c r="O14">
-        <v>6.528272696</v>
+        <v>6.197329578</v>
       </c>
       <c r="P14">
-        <v>23.145694104</v>
+        <v>21.972350322</v>
       </c>
       <c r="Q14">
-        <v>102.145694104</v>
+        <v>100.972350322</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09181719313391612</v>
+        <v>0.09224094820626821</v>
       </c>
       <c r="T14">
-        <v>1.062752728265961</v>
+        <v>1.0725392195443</v>
       </c>
       <c r="U14">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.619978793634473</v>
+        <v>3.19555550293714</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08674936493945334</v>
+        <v>0.08755159992106051</v>
       </c>
       <c r="C15">
-        <v>1254.53690289769</v>
+        <v>1223.25187041238</v>
       </c>
       <c r="D15">
-        <v>1445.72790289769</v>
+        <v>1429.83987041238</v>
       </c>
       <c r="E15">
-        <v>-292.339</v>
+        <v>-276.942</v>
       </c>
       <c r="F15">
-        <v>200.161</v>
+        <v>215.558</v>
       </c>
       <c r="G15">
         <v>8.970000000000001</v>
@@ -2517,45 +2517,45 @@
         <v>41</v>
       </c>
       <c r="M15">
-        <v>12.8303201</v>
+        <v>15.4986202</v>
       </c>
       <c r="N15">
-        <v>28.1696799</v>
+        <v>25.5013798</v>
       </c>
       <c r="O15">
-        <v>6.197329578</v>
+        <v>5.610303555999999</v>
       </c>
       <c r="P15">
-        <v>21.972350322</v>
+        <v>19.891076244</v>
       </c>
       <c r="Q15">
-        <v>100.972350322</v>
+        <v>98.891076244</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09224094820626821</v>
+        <v>0.09267455804774477</v>
       </c>
       <c r="T15">
-        <v>1.0725392195443</v>
+        <v>1.082553303643067</v>
       </c>
       <c r="U15">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.19555550293714</v>
+        <v>2.645396781837392</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08755159992106051</v>
+        <v>0.08801921490266768</v>
       </c>
       <c r="C16">
-        <v>1223.25187041238</v>
+        <v>1198.753963581506</v>
       </c>
       <c r="D16">
-        <v>1429.83987041238</v>
+        <v>1420.738963581505</v>
       </c>
       <c r="E16">
-        <v>-276.942</v>
+        <v>-261.545</v>
       </c>
       <c r="F16">
-        <v>215.558</v>
+        <v>230.955</v>
       </c>
       <c r="G16">
         <v>8.970000000000001</v>
@@ -2599,45 +2599,45 @@
         <v>41</v>
       </c>
       <c r="M16">
-        <v>15.4986202</v>
+        <v>17.50638900000001</v>
       </c>
       <c r="N16">
-        <v>25.5013798</v>
+        <v>23.49361099999999</v>
       </c>
       <c r="O16">
-        <v>5.610303555999999</v>
+        <v>5.168594419999999</v>
       </c>
       <c r="P16">
-        <v>19.891076244</v>
+        <v>18.32501658</v>
       </c>
       <c r="Q16">
-        <v>98.891076244</v>
+        <v>97.32501658</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09267455804774477</v>
+        <v>0.09311837047372667</v>
       </c>
       <c r="T16">
-        <v>1.082553303643067</v>
+        <v>1.092803013250039</v>
       </c>
       <c r="U16">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.645396781837392</v>
+        <v>2.342002111343464</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08801921490266768</v>
+        <v>0.08806094988427485</v>
       </c>
       <c r="C17">
-        <v>1198.753963581506</v>
+        <v>1182.550329212582</v>
       </c>
       <c r="D17">
-        <v>1420.738963581505</v>
+        <v>1419.932329212582</v>
       </c>
       <c r="E17">
-        <v>-261.545</v>
+        <v>-246.148</v>
       </c>
       <c r="F17">
-        <v>230.955</v>
+        <v>246.352</v>
       </c>
       <c r="G17">
         <v>8.970000000000001</v>
@@ -2681,28 +2681,28 @@
         <v>41</v>
       </c>
       <c r="M17">
-        <v>17.506389</v>
+        <v>18.6734816</v>
       </c>
       <c r="N17">
-        <v>23.493611</v>
+        <v>22.3265184</v>
       </c>
       <c r="O17">
-        <v>5.168594420000001</v>
+        <v>4.911834047999999</v>
       </c>
       <c r="P17">
-        <v>18.32501658</v>
+        <v>17.414684352</v>
       </c>
       <c r="Q17">
-        <v>97.32501658</v>
+        <v>96.41468435199999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09311837047372667</v>
+        <v>0.09357274986223196</v>
       </c>
       <c r="T17">
-        <v>1.092803013250039</v>
+        <v>1.103296763561939</v>
       </c>
       <c r="U17">
         <v>0.07580000000000001</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.342002111343465</v>
+        <v>2.195626979384498</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08806094988427485</v>
+        <v>0.08810268486588202</v>
       </c>
       <c r="C18">
-        <v>1182.550329212582</v>
+        <v>1166.347610268399</v>
       </c>
       <c r="D18">
-        <v>1419.932329212582</v>
+        <v>1419.126610268399</v>
       </c>
       <c r="E18">
-        <v>-246.148</v>
+        <v>-230.751</v>
       </c>
       <c r="F18">
-        <v>246.352</v>
+        <v>261.749</v>
       </c>
       <c r="G18">
         <v>8.970000000000001</v>
@@ -2763,28 +2763,28 @@
         <v>41</v>
       </c>
       <c r="M18">
-        <v>18.6734816</v>
+        <v>19.8405742</v>
       </c>
       <c r="N18">
-        <v>22.3265184</v>
+        <v>21.1594258</v>
       </c>
       <c r="O18">
-        <v>4.911834047999999</v>
+        <v>4.655073676</v>
       </c>
       <c r="P18">
-        <v>17.414684352</v>
+        <v>16.504352124</v>
       </c>
       <c r="Q18">
-        <v>96.41468435199999</v>
+        <v>95.50435212399999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09357274986223196</v>
+        <v>0.09403807815166508</v>
       </c>
       <c r="T18">
-        <v>1.103296763561939</v>
+        <v>1.114043375327138</v>
       </c>
       <c r="U18">
         <v>0.07580000000000001</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.195626979384498</v>
+        <v>2.06647245118541</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08810268486588202</v>
+        <v>0.09013809984748919</v>
       </c>
       <c r="C19">
-        <v>1166.347610268399</v>
+        <v>1112.735551610495</v>
       </c>
       <c r="D19">
-        <v>1419.126610268399</v>
+        <v>1380.911551610495</v>
       </c>
       <c r="E19">
-        <v>-230.751</v>
+        <v>-215.354</v>
       </c>
       <c r="F19">
-        <v>261.749</v>
+        <v>277.146</v>
       </c>
       <c r="G19">
         <v>8.970000000000001</v>
@@ -2845,45 +2845,45 @@
         <v>41</v>
       </c>
       <c r="M19">
-        <v>19.8405742</v>
+        <v>24.94314</v>
       </c>
       <c r="N19">
-        <v>21.1594258</v>
+        <v>16.05686</v>
       </c>
       <c r="O19">
-        <v>4.655073676</v>
+        <v>3.5325092</v>
       </c>
       <c r="P19">
-        <v>16.504352124</v>
+        <v>12.5243508</v>
       </c>
       <c r="Q19">
-        <v>95.50435212399999</v>
+        <v>91.52435080000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09403807815166508</v>
+        <v>0.09451475591157217</v>
       </c>
       <c r="T19">
-        <v>1.114043375327138</v>
+        <v>1.125052099574415</v>
       </c>
       <c r="U19">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.06647245118541</v>
+        <v>1.643738518887357</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09013809984748918</v>
+        <v>0.09029059482909636</v>
       </c>
       <c r="C20">
-        <v>1112.735551610496</v>
+        <v>1094.558156454305</v>
       </c>
       <c r="D20">
-        <v>1380.911551610496</v>
+        <v>1378.131156454305</v>
       </c>
       <c r="E20">
-        <v>-215.354</v>
+        <v>-199.957</v>
       </c>
       <c r="F20">
-        <v>277.146</v>
+        <v>292.543</v>
       </c>
       <c r="G20">
         <v>8.970000000000001</v>
@@ -2927,28 +2927,28 @@
         <v>41</v>
       </c>
       <c r="M20">
-        <v>24.94314</v>
+        <v>26.32887</v>
       </c>
       <c r="N20">
-        <v>16.05686</v>
+        <v>14.67113</v>
       </c>
       <c r="O20">
-        <v>3.5325092</v>
+        <v>3.2276486</v>
       </c>
       <c r="P20">
-        <v>12.5243508</v>
+        <v>11.4434814</v>
       </c>
       <c r="Q20">
-        <v>91.52435080000001</v>
+        <v>90.4434814</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09451475591157216</v>
+        <v>0.09500320349271155</v>
       </c>
       <c r="T20">
-        <v>1.125052099574415</v>
+        <v>1.136332644173477</v>
       </c>
       <c r="U20">
         <v>0.09</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>1.643738518887357</v>
+        <v>1.557225965261707</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09029059482909636</v>
+        <v>0.1000750646536888</v>
       </c>
       <c r="C21">
-        <v>1094.558156454305</v>
+        <v>921.4920242017911</v>
       </c>
       <c r="D21">
-        <v>1378.131156454305</v>
+        <v>1220.462024201791</v>
       </c>
       <c r="E21">
-        <v>-199.957</v>
+        <v>-184.5599999999999</v>
       </c>
       <c r="F21">
-        <v>292.543</v>
+        <v>307.9400000000001</v>
       </c>
       <c r="G21">
         <v>8.970000000000001</v>
@@ -3009,45 +3009,45 @@
         <v>41</v>
       </c>
       <c r="M21">
-        <v>26.32887</v>
+        <v>45.20559200000001</v>
       </c>
       <c r="N21">
-        <v>14.67113</v>
+        <v>-4.20559200000001</v>
       </c>
       <c r="O21">
-        <v>3.2276486</v>
+        <v>-0.9252302400000022</v>
       </c>
       <c r="P21">
-        <v>11.4434814</v>
+        <v>-3.280361760000008</v>
       </c>
       <c r="Q21">
-        <v>90.4434814</v>
+        <v>75.71963823999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09500320349271155</v>
+        <v>0.09571668591875412</v>
       </c>
       <c r="T21">
-        <v>1.136332644173477</v>
+        <v>1.152810298354599</v>
       </c>
       <c r="U21">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.22</v>
+        <v>0.1995328365570347</v>
       </c>
       <c r="W21">
-        <v>0.0702</v>
+        <v>0.1175085795934273</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y21">
-        <v>1.557225965261707</v>
+        <v>0.9069674388956126</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1000750646536888</v>
+        <v>0.1010850646536888</v>
       </c>
       <c r="C22">
-        <v>921.4920242017911</v>
+        <v>891.849920404673</v>
       </c>
       <c r="D22">
-        <v>1220.462024201791</v>
+        <v>1206.216920404673</v>
       </c>
       <c r="E22">
-        <v>-184.5599999999999</v>
+        <v>-169.163</v>
       </c>
       <c r="F22">
-        <v>307.9400000000001</v>
+        <v>323.337</v>
       </c>
       <c r="G22">
         <v>8.970000000000001</v>
@@ -3091,37 +3091,37 @@
         <v>41</v>
       </c>
       <c r="M22">
-        <v>45.20559200000001</v>
+        <v>47.46587160000001</v>
       </c>
       <c r="N22">
-        <v>-4.20559200000001</v>
+        <v>-6.465871600000014</v>
       </c>
       <c r="O22">
-        <v>-0.9252302400000022</v>
+        <v>-1.422491752000003</v>
       </c>
       <c r="P22">
-        <v>-3.280361760000008</v>
+        <v>-5.043379848000011</v>
       </c>
       <c r="Q22">
-        <v>75.71963823999999</v>
+        <v>73.95662015199999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09571668591875412</v>
+        <v>0.09634854270253582</v>
       </c>
       <c r="T22">
-        <v>1.152810298354599</v>
+        <v>1.167402833776809</v>
       </c>
       <c r="U22">
         <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.1995328365570347</v>
+        <v>0.1900312729114617</v>
       </c>
       <c r="W22">
-        <v>0.1175085795934273</v>
+        <v>0.1189034091365974</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.9069674388956126</v>
+        <v>0.8637785132339166</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1010850646536887</v>
+        <v>0.1020950646536888</v>
       </c>
       <c r="C23">
-        <v>891.8499204046732</v>
+        <v>862.5365147702024</v>
       </c>
       <c r="D23">
-        <v>1206.216920404673</v>
+        <v>1192.300514770202</v>
       </c>
       <c r="E23">
-        <v>-169.163</v>
+        <v>-153.766</v>
       </c>
       <c r="F23">
-        <v>323.337</v>
+        <v>338.734</v>
       </c>
       <c r="G23">
         <v>8.970000000000001</v>
@@ -3173,37 +3173,37 @@
         <v>41</v>
       </c>
       <c r="M23">
-        <v>47.4658716</v>
+        <v>49.72615120000001</v>
       </c>
       <c r="N23">
-        <v>-6.4658716</v>
+        <v>-8.726151200000011</v>
       </c>
       <c r="O23">
-        <v>-1.422491752</v>
+        <v>-1.919753264000002</v>
       </c>
       <c r="P23">
-        <v>-5.043379848</v>
+        <v>-6.806397936000009</v>
       </c>
       <c r="Q23">
-        <v>73.956620152</v>
+        <v>72.19360206399999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09634854270253582</v>
+        <v>0.09699660094231191</v>
       </c>
       <c r="T23">
-        <v>1.167402833776809</v>
+        <v>1.182369536773947</v>
       </c>
       <c r="U23">
         <v>0.1468</v>
       </c>
       <c r="V23">
-        <v>0.1900312729114617</v>
+        <v>0.1813934877791225</v>
       </c>
       <c r="W23">
-        <v>0.1189034091365974</v>
+        <v>0.1201714359940248</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.8637785132339169</v>
+        <v>0.8245158535414659</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1020950646536888</v>
+        <v>0.1159714363566373</v>
       </c>
       <c r="C24">
-        <v>862.5365147702024</v>
+        <v>684.0063655715833</v>
       </c>
       <c r="D24">
-        <v>1192.300514770202</v>
+        <v>1029.167365571583</v>
       </c>
       <c r="E24">
-        <v>-153.766</v>
+        <v>-138.369</v>
       </c>
       <c r="F24">
-        <v>338.734</v>
+        <v>354.131</v>
       </c>
       <c r="G24">
         <v>8.970000000000001</v>
@@ -3255,45 +3255,45 @@
         <v>41</v>
       </c>
       <c r="M24">
-        <v>49.72615120000001</v>
+        <v>71.10950480000001</v>
       </c>
       <c r="N24">
-        <v>-8.726151200000011</v>
+        <v>-30.10950480000001</v>
       </c>
       <c r="O24">
-        <v>-1.919753264000002</v>
+        <v>-6.624091056000002</v>
       </c>
       <c r="P24">
-        <v>-6.806397936000009</v>
+        <v>-23.48541374400001</v>
       </c>
       <c r="Q24">
-        <v>72.19360206399999</v>
+        <v>55.51458625599999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09699660094231191</v>
+        <v>0.09824119537396345</v>
       </c>
       <c r="T24">
-        <v>1.182369536773947</v>
+        <v>1.211113057135415</v>
       </c>
       <c r="U24">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.1813934877791225</v>
+        <v>0.1268466153064815</v>
       </c>
       <c r="W24">
-        <v>0.1201714359940248</v>
+        <v>0.1753291996464585</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y24">
-        <v>0.8245158535414659</v>
+        <v>0.5765755241203704</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1159714363566373</v>
+        <v>0.1175214363566373</v>
       </c>
       <c r="C25">
-        <v>684.0063655715833</v>
+        <v>653.1172367608643</v>
       </c>
       <c r="D25">
-        <v>1029.167365571583</v>
+        <v>1013.675236760864</v>
       </c>
       <c r="E25">
-        <v>-138.369</v>
+        <v>-122.972</v>
       </c>
       <c r="F25">
-        <v>354.131</v>
+        <v>369.528</v>
       </c>
       <c r="G25">
         <v>8.970000000000001</v>
@@ -3337,37 +3337,37 @@
         <v>41</v>
       </c>
       <c r="M25">
-        <v>71.10950480000001</v>
+        <v>74.20122240000001</v>
       </c>
       <c r="N25">
-        <v>-30.10950480000001</v>
+        <v>-33.20122240000001</v>
       </c>
       <c r="O25">
-        <v>-6.624091056000002</v>
+        <v>-7.304268928000002</v>
       </c>
       <c r="P25">
-        <v>-23.48541374400001</v>
+        <v>-25.896953472</v>
       </c>
       <c r="Q25">
-        <v>55.51458625599999</v>
+        <v>53.10304652799999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09824119537396345</v>
+        <v>0.09893121110256824</v>
       </c>
       <c r="T25">
-        <v>1.211113057135415</v>
+        <v>1.227048755255618</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1268466153064815</v>
+        <v>0.1215613396687114</v>
       </c>
       <c r="W25">
-        <v>0.1753291996464585</v>
+        <v>0.1763904829945228</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.5765755241203704</v>
+        <v>0.5525515439486883</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1175214363566373</v>
+        <v>0.1190714363566373</v>
       </c>
       <c r="C26">
-        <v>653.1172367608643</v>
+        <v>622.6875994043055</v>
       </c>
       <c r="D26">
-        <v>1013.675236760864</v>
+        <v>998.6425994043054</v>
       </c>
       <c r="E26">
-        <v>-122.972</v>
+        <v>-107.575</v>
       </c>
       <c r="F26">
-        <v>369.528</v>
+        <v>384.925</v>
       </c>
       <c r="G26">
         <v>8.970000000000001</v>
@@ -3419,37 +3419,37 @@
         <v>41</v>
       </c>
       <c r="M26">
-        <v>74.20122240000001</v>
+        <v>77.29294</v>
       </c>
       <c r="N26">
-        <v>-33.20122240000001</v>
+        <v>-36.29294</v>
       </c>
       <c r="O26">
-        <v>-7.304268928000002</v>
+        <v>-7.984446800000001</v>
       </c>
       <c r="P26">
-        <v>-25.896953472</v>
+        <v>-28.3084932</v>
       </c>
       <c r="Q26">
-        <v>53.10304652799999</v>
+        <v>50.6915068</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09893121110256824</v>
+        <v>0.09963962725060248</v>
       </c>
       <c r="T26">
-        <v>1.227048755255618</v>
+        <v>1.243409405325692</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1215613396687114</v>
+        <v>0.116698886081963</v>
       </c>
       <c r="W26">
-        <v>0.1763904829945228</v>
+        <v>0.1773668636747418</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5525515439486883</v>
+        <v>0.5304494821907408</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1190714363566373</v>
+        <v>0.1206214363566373</v>
       </c>
       <c r="C27">
-        <v>622.6875994043055</v>
+        <v>592.6973096829292</v>
       </c>
       <c r="D27">
-        <v>998.6425994043054</v>
+        <v>984.0493096829292</v>
       </c>
       <c r="E27">
-        <v>-107.575</v>
+        <v>-92.178</v>
       </c>
       <c r="F27">
-        <v>384.925</v>
+        <v>400.322</v>
       </c>
       <c r="G27">
         <v>8.970000000000001</v>
@@ -3501,37 +3501,37 @@
         <v>41</v>
       </c>
       <c r="M27">
-        <v>77.29294</v>
+        <v>80.3846576</v>
       </c>
       <c r="N27">
-        <v>-36.29294</v>
+        <v>-39.3846576</v>
       </c>
       <c r="O27">
-        <v>-7.984446800000001</v>
+        <v>-8.664624671999999</v>
       </c>
       <c r="P27">
-        <v>-28.3084932</v>
+        <v>-30.720032928</v>
       </c>
       <c r="Q27">
-        <v>50.6915068</v>
+        <v>48.27996707200001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09963962725060248</v>
+        <v>0.100367189781016</v>
       </c>
       <c r="T27">
-        <v>1.243409405325692</v>
+        <v>1.260212235127391</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.116698886081963</v>
+        <v>0.1122104673865029</v>
       </c>
       <c r="W27">
-        <v>0.1773668636747418</v>
+        <v>0.1782681381487902</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.5304494821907408</v>
+        <v>0.5100475790295584</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1206214363566373</v>
+        <v>0.1318015527303493</v>
       </c>
       <c r="C28">
-        <v>592.6973096829292</v>
+        <v>483.4677616328172</v>
       </c>
       <c r="D28">
-        <v>984.0493096829292</v>
+        <v>890.2167616328172</v>
       </c>
       <c r="E28">
-        <v>-92.178</v>
+        <v>-76.78099999999995</v>
       </c>
       <c r="F28">
-        <v>400.322</v>
+        <v>415.7190000000001</v>
       </c>
       <c r="G28">
         <v>8.970000000000001</v>
@@ -3583,45 +3583,45 @@
         <v>41</v>
       </c>
       <c r="M28">
-        <v>80.3846576</v>
+        <v>98.02654020000001</v>
       </c>
       <c r="N28">
-        <v>-39.3846576</v>
+        <v>-57.02654020000001</v>
       </c>
       <c r="O28">
-        <v>-8.664624671999999</v>
+        <v>-12.545838844</v>
       </c>
       <c r="P28">
-        <v>-30.720032928</v>
+        <v>-44.48070135600001</v>
       </c>
       <c r="Q28">
-        <v>48.27996707200001</v>
+        <v>34.51929864399999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.100367189781016</v>
+        <v>0.1013614202899505</v>
       </c>
       <c r="T28">
-        <v>1.260212235127391</v>
+        <v>1.283173678751744</v>
       </c>
       <c r="U28">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.1122104673865029</v>
+        <v>0.09201589673160779</v>
       </c>
       <c r="W28">
-        <v>0.1782681381487902</v>
+        <v>0.2141026515506869</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.5100475790295584</v>
+        <v>0.4182540760527627</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1318015527303493</v>
+        <v>0.1337015527303493</v>
       </c>
       <c r="C29">
-        <v>483.4677616328172</v>
+        <v>453.8750082159565</v>
       </c>
       <c r="D29">
-        <v>890.2167616328172</v>
+        <v>876.0210082159565</v>
       </c>
       <c r="E29">
-        <v>-76.78099999999995</v>
+        <v>-61.38399999999996</v>
       </c>
       <c r="F29">
-        <v>415.7190000000001</v>
+        <v>431.116</v>
       </c>
       <c r="G29">
         <v>8.970000000000001</v>
@@ -3665,37 +3665,37 @@
         <v>41</v>
       </c>
       <c r="M29">
-        <v>98.02654020000001</v>
+        <v>101.6571528</v>
       </c>
       <c r="N29">
-        <v>-57.02654020000001</v>
+        <v>-60.65715280000002</v>
       </c>
       <c r="O29">
-        <v>-12.545838844</v>
+        <v>-13.34457361600001</v>
       </c>
       <c r="P29">
-        <v>-44.48070135600001</v>
+        <v>-47.31257918400001</v>
       </c>
       <c r="Q29">
-        <v>34.51929864399999</v>
+        <v>31.68742081599999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1013614202899505</v>
+        <v>0.1021331066828665</v>
       </c>
       <c r="T29">
-        <v>1.283173678751744</v>
+        <v>1.300995535401073</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.09201589673160779</v>
+        <v>0.08872961470547892</v>
       </c>
       <c r="W29">
-        <v>0.2141026515506869</v>
+        <v>0.2148775568524481</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.4182540760527627</v>
+        <v>0.4033164304794497</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1337015527303493</v>
+        <v>0.1356015527303493</v>
       </c>
       <c r="C30">
-        <v>453.8750082159565</v>
+        <v>424.7278908594533</v>
       </c>
       <c r="D30">
-        <v>876.0210082159565</v>
+        <v>862.2708908594534</v>
       </c>
       <c r="E30">
-        <v>-61.38399999999996</v>
+        <v>-45.98699999999991</v>
       </c>
       <c r="F30">
-        <v>431.116</v>
+        <v>446.5130000000001</v>
       </c>
       <c r="G30">
         <v>8.970000000000001</v>
@@ -3747,37 +3747,37 @@
         <v>41</v>
       </c>
       <c r="M30">
-        <v>101.6571528</v>
+        <v>105.2877654</v>
       </c>
       <c r="N30">
-        <v>-60.65715280000002</v>
+        <v>-64.28776540000003</v>
       </c>
       <c r="O30">
-        <v>-13.34457361600001</v>
+        <v>-14.14330838800001</v>
       </c>
       <c r="P30">
-        <v>-47.31257918400001</v>
+        <v>-50.14445701200002</v>
       </c>
       <c r="Q30">
-        <v>31.68742081599999</v>
+        <v>28.85554298799998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1021331066828665</v>
+        <v>0.1029265307206533</v>
       </c>
       <c r="T30">
-        <v>1.300995535401073</v>
+        <v>1.31931941618137</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.08872961470547892</v>
+        <v>0.08566997281908309</v>
       </c>
       <c r="W30">
-        <v>0.2148775568524481</v>
+        <v>0.2155990204092602</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.4033164304794497</v>
+        <v>0.3894089673594686</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1356015527303493</v>
+        <v>0.1375015527303493</v>
       </c>
       <c r="C31">
-        <v>424.7278908594537</v>
+        <v>396.0057495937308</v>
       </c>
       <c r="D31">
-        <v>862.2708908594536</v>
+        <v>848.9457495937307</v>
       </c>
       <c r="E31">
-        <v>-45.98700000000002</v>
+        <v>-30.59000000000003</v>
       </c>
       <c r="F31">
-        <v>446.513</v>
+        <v>461.91</v>
       </c>
       <c r="G31">
         <v>8.970000000000001</v>
@@ -3829,37 +3829,37 @@
         <v>41</v>
       </c>
       <c r="M31">
-        <v>105.2877654</v>
+        <v>108.918378</v>
       </c>
       <c r="N31">
-        <v>-64.2877654</v>
+        <v>-67.91837799999999</v>
       </c>
       <c r="O31">
-        <v>-14.143308388</v>
+        <v>-14.94204316</v>
       </c>
       <c r="P31">
-        <v>-50.144457012</v>
+        <v>-52.97633483999999</v>
       </c>
       <c r="Q31">
-        <v>28.855542988</v>
+        <v>26.02366516000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1029265307206533</v>
+        <v>0.1037426240166627</v>
       </c>
       <c r="T31">
-        <v>1.31931941618137</v>
+        <v>1.338166836412533</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.08566997281908312</v>
+        <v>0.08281430705844701</v>
       </c>
       <c r="W31">
-        <v>0.2155990204092602</v>
+        <v>0.2162723863956182</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3894089673594687</v>
+        <v>0.3764286684474865</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1375015527303493</v>
+        <v>0.1394015527303493</v>
       </c>
       <c r="C32">
-        <v>396.0057495937308</v>
+        <v>367.6891820931621</v>
       </c>
       <c r="D32">
-        <v>848.9457495937307</v>
+        <v>836.0261820931621</v>
       </c>
       <c r="E32">
-        <v>-30.59000000000003</v>
+        <v>-15.19299999999998</v>
       </c>
       <c r="F32">
-        <v>461.91</v>
+        <v>477.307</v>
       </c>
       <c r="G32">
         <v>8.970000000000001</v>
@@ -3911,37 +3911,37 @@
         <v>41</v>
       </c>
       <c r="M32">
-        <v>108.918378</v>
+        <v>112.5489906</v>
       </c>
       <c r="N32">
-        <v>-67.91837799999999</v>
+        <v>-71.54899060000001</v>
       </c>
       <c r="O32">
-        <v>-14.94204316</v>
+        <v>-15.740777932</v>
       </c>
       <c r="P32">
-        <v>-52.97633483999999</v>
+        <v>-55.80821266800001</v>
       </c>
       <c r="Q32">
-        <v>26.02366516000001</v>
+        <v>23.19178733199999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1037426240166627</v>
+        <v>0.1045823721908172</v>
       </c>
       <c r="T32">
-        <v>1.338166836412533</v>
+        <v>1.357560558679381</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.08281430705844701</v>
+        <v>0.0801428777984971</v>
       </c>
       <c r="W32">
-        <v>0.2162723863956182</v>
+        <v>0.2169023094151144</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3764286684474865</v>
+        <v>0.3642858081749868</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1394015527303493</v>
+        <v>0.1413015527303493</v>
       </c>
       <c r="C33">
-        <v>367.6891820931621</v>
+        <v>339.7599494141513</v>
       </c>
       <c r="D33">
-        <v>836.0261820931621</v>
+        <v>823.4939494141513</v>
       </c>
       <c r="E33">
-        <v>-15.19299999999998</v>
+        <v>0.2040000000000077</v>
       </c>
       <c r="F33">
-        <v>477.307</v>
+        <v>492.704</v>
       </c>
       <c r="G33">
         <v>8.970000000000001</v>
@@ -3993,37 +3993,37 @@
         <v>41</v>
       </c>
       <c r="M33">
-        <v>112.5489906</v>
+        <v>116.1796032</v>
       </c>
       <c r="N33">
-        <v>-71.54899060000001</v>
+        <v>-75.1796032</v>
       </c>
       <c r="O33">
-        <v>-15.740777932</v>
+        <v>-16.539512704</v>
       </c>
       <c r="P33">
-        <v>-55.80821266800001</v>
+        <v>-58.640090496</v>
       </c>
       <c r="Q33">
-        <v>23.19178733199999</v>
+        <v>20.359909504</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1045823721908172</v>
+        <v>0.1054468188406822</v>
       </c>
       <c r="T33">
-        <v>1.357560558679381</v>
+        <v>1.377524684542313</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.0801428777984971</v>
+        <v>0.07763841286729407</v>
       </c>
       <c r="W33">
-        <v>0.2169023094151144</v>
+        <v>0.2174928622458921</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3642858081749868</v>
+        <v>0.3529018766695186</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1413015527303493</v>
+        <v>0.1432015527303493</v>
       </c>
       <c r="C34">
-        <v>339.7599494141513</v>
+        <v>312.2008900860537</v>
       </c>
       <c r="D34">
-        <v>823.4939494141513</v>
+        <v>811.3318900860537</v>
       </c>
       <c r="E34">
-        <v>0.2040000000000077</v>
+        <v>15.60100000000006</v>
       </c>
       <c r="F34">
-        <v>492.704</v>
+        <v>508.1010000000001</v>
       </c>
       <c r="G34">
         <v>8.970000000000001</v>
@@ -4075,37 +4075,37 @@
         <v>41</v>
       </c>
       <c r="M34">
-        <v>116.1796032</v>
+        <v>119.8102158</v>
       </c>
       <c r="N34">
-        <v>-75.1796032</v>
+        <v>-78.81021580000002</v>
       </c>
       <c r="O34">
-        <v>-16.539512704</v>
+        <v>-17.33824747600001</v>
       </c>
       <c r="P34">
-        <v>-58.640090496</v>
+        <v>-61.47196832400002</v>
       </c>
       <c r="Q34">
-        <v>20.359909504</v>
+        <v>17.52803167599998</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1054468188406822</v>
+        <v>0.106337069868155</v>
       </c>
       <c r="T34">
-        <v>1.377524684542313</v>
+        <v>1.398084754460855</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.07763841286729407</v>
+        <v>0.07528573368949727</v>
       </c>
       <c r="W34">
-        <v>0.2174928622458921</v>
+        <v>0.2180476239960165</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3529018766695186</v>
+        <v>0.3422078804068058</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1432015527303493</v>
+        <v>0.1451015527303493</v>
       </c>
       <c r="C35">
-        <v>312.2008900860537</v>
+        <v>284.9958417039738</v>
       </c>
       <c r="D35">
-        <v>811.3318900860537</v>
+        <v>799.5238417039739</v>
       </c>
       <c r="E35">
-        <v>15.60100000000006</v>
+        <v>30.99800000000005</v>
       </c>
       <c r="F35">
-        <v>508.1010000000001</v>
+        <v>523.498</v>
       </c>
       <c r="G35">
         <v>8.970000000000001</v>
@@ -4157,37 +4157,37 @@
         <v>41</v>
       </c>
       <c r="M35">
-        <v>119.8102158</v>
+        <v>123.4408284</v>
       </c>
       <c r="N35">
-        <v>-78.81021580000002</v>
+        <v>-82.44082840000002</v>
       </c>
       <c r="O35">
-        <v>-17.33824747600001</v>
+        <v>-18.136982248</v>
       </c>
       <c r="P35">
-        <v>-61.47196832400002</v>
+        <v>-64.30384615200001</v>
       </c>
       <c r="Q35">
-        <v>17.52803167599998</v>
+        <v>14.69615384799999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.106337069868155</v>
+        <v>0.1072542981994907</v>
       </c>
       <c r="T35">
-        <v>1.398084754460855</v>
+        <v>1.419267856801171</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.07528573368949727</v>
+        <v>0.07307144740451206</v>
       </c>
       <c r="W35">
-        <v>0.2180476239960165</v>
+        <v>0.2185697527020161</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3422078804068058</v>
+        <v>0.3321429427477821</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1451015527303493</v>
+        <v>0.1470015527303493</v>
       </c>
       <c r="C36">
-        <v>284.9958417039738</v>
+        <v>258.1295692701317</v>
       </c>
       <c r="D36">
-        <v>799.5238417039739</v>
+        <v>788.0545692701318</v>
       </c>
       <c r="E36">
-        <v>30.99800000000005</v>
+        <v>46.3950000000001</v>
       </c>
       <c r="F36">
-        <v>523.498</v>
+        <v>538.8950000000001</v>
       </c>
       <c r="G36">
         <v>8.970000000000001</v>
@@ -4239,37 +4239,37 @@
         <v>41</v>
       </c>
       <c r="M36">
-        <v>123.4408284</v>
+        <v>127.071441</v>
       </c>
       <c r="N36">
-        <v>-82.44082840000002</v>
+        <v>-86.07144100000002</v>
       </c>
       <c r="O36">
-        <v>-18.136982248</v>
+        <v>-18.93571702000001</v>
       </c>
       <c r="P36">
-        <v>-64.30384615200001</v>
+        <v>-67.13572398000002</v>
       </c>
       <c r="Q36">
-        <v>14.69615384799999</v>
+        <v>11.86427601999998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1072542981994907</v>
+        <v>0.1081997489410213</v>
       </c>
       <c r="T36">
-        <v>1.419267856801171</v>
+        <v>1.441102746905804</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.07307144740451206</v>
+        <v>0.07098369176438314</v>
       </c>
       <c r="W36">
-        <v>0.2185697527020161</v>
+        <v>0.2190620454819585</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3321429427477821</v>
+        <v>0.3226531443835597</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1470015527303493</v>
+        <v>0.1489015527303493</v>
       </c>
       <c r="C37">
-        <v>258.1295692701317</v>
+        <v>231.5876996157176</v>
       </c>
       <c r="D37">
-        <v>788.0545692701318</v>
+        <v>776.9096996157176</v>
       </c>
       <c r="E37">
-        <v>46.3950000000001</v>
+        <v>61.79200000000003</v>
       </c>
       <c r="F37">
-        <v>538.8950000000001</v>
+        <v>554.292</v>
       </c>
       <c r="G37">
         <v>8.970000000000001</v>
@@ -4321,37 +4321,37 @@
         <v>41</v>
       </c>
       <c r="M37">
-        <v>127.071441</v>
+        <v>130.7020536</v>
       </c>
       <c r="N37">
-        <v>-86.07144100000002</v>
+        <v>-89.7020536</v>
       </c>
       <c r="O37">
-        <v>-18.93571702000001</v>
+        <v>-19.734451792</v>
       </c>
       <c r="P37">
-        <v>-67.13572398000002</v>
+        <v>-69.967601808</v>
       </c>
       <c r="Q37">
-        <v>11.86427601999998</v>
+        <v>9.032398192000002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1081997489410213</v>
+        <v>0.1091747450182248</v>
       </c>
       <c r="T37">
-        <v>1.441102746905804</v>
+        <v>1.463619977326208</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.07098369176438314</v>
+        <v>0.06901192254870585</v>
       </c>
       <c r="W37">
-        <v>0.2190620454819585</v>
+        <v>0.2195269886630152</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3226531443835597</v>
+        <v>0.313690557039572</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1489015527303493</v>
+        <v>0.1508015527303493</v>
       </c>
       <c r="C38">
-        <v>231.5876996157176</v>
+        <v>205.3566613096867</v>
       </c>
       <c r="D38">
-        <v>776.9096996157176</v>
+        <v>766.0756613096867</v>
       </c>
       <c r="E38">
-        <v>61.79200000000003</v>
+        <v>77.18899999999996</v>
       </c>
       <c r="F38">
-        <v>554.292</v>
+        <v>569.689</v>
       </c>
       <c r="G38">
         <v>8.970000000000001</v>
@@ -4403,37 +4403,37 @@
         <v>41</v>
       </c>
       <c r="M38">
-        <v>130.7020536</v>
+        <v>134.3326662</v>
       </c>
       <c r="N38">
-        <v>-89.7020536</v>
+        <v>-93.33266620000001</v>
       </c>
       <c r="O38">
-        <v>-19.734451792</v>
+        <v>-20.533186564</v>
       </c>
       <c r="P38">
-        <v>-69.967601808</v>
+        <v>-72.799479636</v>
       </c>
       <c r="Q38">
-        <v>9.032398192000002</v>
+        <v>6.200520363999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1091747450182248</v>
+        <v>0.1101806933518474</v>
       </c>
       <c r="T38">
-        <v>1.463619977326208</v>
+        <v>1.48685204045837</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.06901192254870585</v>
+        <v>0.06714673545279487</v>
       </c>
       <c r="W38">
-        <v>0.2195269886630152</v>
+        <v>0.219966799780231</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.313690557039572</v>
+        <v>0.3052124338763403</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1508015527303493</v>
+        <v>0.1527015527303493</v>
       </c>
       <c r="C39">
-        <v>205.3566613096867</v>
+        <v>179.4236295262497</v>
       </c>
       <c r="D39">
-        <v>766.0756613096867</v>
+        <v>755.5396295262497</v>
       </c>
       <c r="E39">
-        <v>77.18899999999996</v>
+        <v>92.58600000000001</v>
       </c>
       <c r="F39">
-        <v>569.689</v>
+        <v>585.086</v>
       </c>
       <c r="G39">
         <v>8.970000000000001</v>
@@ -4485,37 +4485,37 @@
         <v>41</v>
       </c>
       <c r="M39">
-        <v>134.3326662</v>
+        <v>137.9632788</v>
       </c>
       <c r="N39">
-        <v>-93.33266620000001</v>
+        <v>-96.96327880000001</v>
       </c>
       <c r="O39">
-        <v>-20.533186564</v>
+        <v>-21.331921336</v>
       </c>
       <c r="P39">
-        <v>-72.799479636</v>
+        <v>-75.631357464</v>
       </c>
       <c r="Q39">
-        <v>6.200520363999999</v>
+        <v>3.368642535999996</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1101806933518474</v>
+        <v>0.1112190916317159</v>
       </c>
       <c r="T39">
-        <v>1.48685204045837</v>
+        <v>1.510833524981892</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.06714673545279487</v>
+        <v>0.06537971609877395</v>
       </c>
       <c r="W39">
-        <v>0.219966799780231</v>
+        <v>0.2203834629439091</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3052124338763403</v>
+        <v>0.2971805277216998</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1527015527303493</v>
+        <v>0.1546015527303493</v>
       </c>
       <c r="C40">
-        <v>179.4236295262497</v>
+        <v>153.776475400151</v>
       </c>
       <c r="D40">
-        <v>755.5396295262497</v>
+        <v>745.289475400151</v>
       </c>
       <c r="E40">
-        <v>92.58600000000001</v>
+        <v>107.9830000000001</v>
       </c>
       <c r="F40">
-        <v>585.086</v>
+        <v>600.4830000000001</v>
       </c>
       <c r="G40">
         <v>8.970000000000001</v>
@@ -4567,37 +4567,37 @@
         <v>41</v>
       </c>
       <c r="M40">
-        <v>137.9632788</v>
+        <v>141.5938914</v>
       </c>
       <c r="N40">
-        <v>-96.96327880000001</v>
+        <v>-100.5938914</v>
       </c>
       <c r="O40">
-        <v>-21.331921336</v>
+        <v>-22.130656108</v>
       </c>
       <c r="P40">
-        <v>-75.631357464</v>
+        <v>-78.46323529200001</v>
       </c>
       <c r="Q40">
-        <v>3.368642535999996</v>
+        <v>0.5367647079999927</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1112190916317159</v>
+        <v>0.112291535756826</v>
       </c>
       <c r="T40">
-        <v>1.510833524981892</v>
+        <v>1.535601287686513</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.06537971609877395</v>
+        <v>0.06370331312188231</v>
       </c>
       <c r="W40">
-        <v>0.2203834629439091</v>
+        <v>0.2207787587658602</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2971805277216998</v>
+        <v>0.2895605141903741</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1546015527303493</v>
+        <v>0.1565015527303493</v>
       </c>
       <c r="C41">
-        <v>153.776475400151</v>
+        <v>128.4037194492478</v>
       </c>
       <c r="D41">
-        <v>745.289475400151</v>
+        <v>735.3137194492479</v>
       </c>
       <c r="E41">
-        <v>107.9830000000001</v>
+        <v>123.3800000000001</v>
       </c>
       <c r="F41">
-        <v>600.4830000000001</v>
+        <v>615.8800000000001</v>
       </c>
       <c r="G41">
         <v>8.970000000000001</v>
@@ -4649,37 +4649,37 @@
         <v>41</v>
       </c>
       <c r="M41">
-        <v>141.5938914</v>
+        <v>145.224504</v>
       </c>
       <c r="N41">
-        <v>-100.5938914</v>
+        <v>-104.224504</v>
       </c>
       <c r="O41">
-        <v>-22.130656108</v>
+        <v>-22.92939088000001</v>
       </c>
       <c r="P41">
-        <v>-78.46323529200001</v>
+        <v>-81.29511312000002</v>
       </c>
       <c r="Q41">
-        <v>0.5367647079999927</v>
+        <v>-2.295113120000025</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.112291535756826</v>
+        <v>0.1133997280194398</v>
       </c>
       <c r="T41">
-        <v>1.535601287686513</v>
+        <v>1.561194642481288</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.06370331312188231</v>
+        <v>0.06211073029383525</v>
       </c>
       <c r="W41">
-        <v>0.2207787587658602</v>
+        <v>0.2211542897967136</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2895605141903741</v>
+        <v>0.2823215013356147</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1565015527303493</v>
+        <v>0.1584015527303493</v>
       </c>
       <c r="C42">
-        <v>128.4037194492478</v>
+        <v>103.2944886883338</v>
       </c>
       <c r="D42">
-        <v>735.3137194492479</v>
+        <v>725.6014886883338</v>
       </c>
       <c r="E42">
-        <v>123.3800000000001</v>
+        <v>138.777</v>
       </c>
       <c r="F42">
-        <v>615.8800000000001</v>
+        <v>631.277</v>
       </c>
       <c r="G42">
         <v>8.970000000000001</v>
@@ -4731,37 +4731,37 @@
         <v>41</v>
       </c>
       <c r="M42">
-        <v>145.224504</v>
+        <v>148.8551166</v>
       </c>
       <c r="N42">
-        <v>-104.224504</v>
+        <v>-107.8551166</v>
       </c>
       <c r="O42">
-        <v>-22.92939088000001</v>
+        <v>-23.728125652</v>
       </c>
       <c r="P42">
-        <v>-81.29511312000002</v>
+        <v>-84.126990948</v>
       </c>
       <c r="Q42">
-        <v>-2.295113120000025</v>
+        <v>-5.126990948</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1133997280194398</v>
+        <v>0.1145454861214642</v>
       </c>
       <c r="T42">
-        <v>1.561194642481288</v>
+        <v>1.587655568625039</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06211073029383525</v>
+        <v>0.06059583443301</v>
       </c>
       <c r="W42">
-        <v>0.2211542897967136</v>
+        <v>0.2215115022406963</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2823215013356147</v>
+        <v>0.2754356110591364</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1584015527303493</v>
+        <v>0.1603015527303493</v>
       </c>
       <c r="C43">
-        <v>103.2944886883338</v>
+        <v>78.43847709737383</v>
       </c>
       <c r="D43">
-        <v>725.6014886883338</v>
+        <v>716.1424770973739</v>
       </c>
       <c r="E43">
-        <v>138.777</v>
+        <v>154.1740000000001</v>
       </c>
       <c r="F43">
-        <v>631.277</v>
+        <v>646.6740000000001</v>
       </c>
       <c r="G43">
         <v>8.970000000000001</v>
@@ -4813,37 +4813,37 @@
         <v>41</v>
       </c>
       <c r="M43">
-        <v>148.8551166</v>
+        <v>152.4857292</v>
       </c>
       <c r="N43">
-        <v>-107.8551166</v>
+        <v>-111.4857292</v>
       </c>
       <c r="O43">
-        <v>-23.728125652</v>
+        <v>-24.52686042400001</v>
       </c>
       <c r="P43">
-        <v>-84.126990948</v>
+        <v>-86.95886877600003</v>
       </c>
       <c r="Q43">
-        <v>-5.126990948</v>
+        <v>-7.958868776000031</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1145454861214642</v>
+        <v>0.1157307531235584</v>
       </c>
       <c r="T43">
-        <v>1.587655568625039</v>
+        <v>1.615028940497884</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06059583443301</v>
+        <v>0.05915307647031928</v>
       </c>
       <c r="W43">
-        <v>0.2215115022406963</v>
+        <v>0.2218517045682987</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2754356110591364</v>
+        <v>0.2688776203196331</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1603015527303493</v>
+        <v>0.1622015527303493</v>
       </c>
       <c r="C44">
-        <v>78.43847709737395</v>
+        <v>53.82590914198943</v>
       </c>
       <c r="D44">
-        <v>716.1424770973739</v>
+        <v>706.9269091419894</v>
       </c>
       <c r="E44">
-        <v>154.174</v>
+        <v>169.571</v>
       </c>
       <c r="F44">
-        <v>646.674</v>
+        <v>662.071</v>
       </c>
       <c r="G44">
         <v>8.970000000000001</v>
@@ -4895,37 +4895,37 @@
         <v>41</v>
       </c>
       <c r="M44">
-        <v>152.4857292</v>
+        <v>156.1163418</v>
       </c>
       <c r="N44">
-        <v>-111.4857292</v>
+        <v>-115.1163418</v>
       </c>
       <c r="O44">
-        <v>-24.526860424</v>
+        <v>-25.325595196</v>
       </c>
       <c r="P44">
-        <v>-86.958868776</v>
+        <v>-89.79074660400002</v>
       </c>
       <c r="Q44">
-        <v>-7.958868776000003</v>
+        <v>-10.79074660400002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1157307531235584</v>
+        <v>0.1169576084415155</v>
       </c>
       <c r="T44">
-        <v>1.615028940497884</v>
+        <v>1.643362781559251</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.05915307647031929</v>
+        <v>0.05777742352914908</v>
       </c>
       <c r="W44">
-        <v>0.2218517045682987</v>
+        <v>0.2221760835318267</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2688776203196331</v>
+        <v>0.262624652405223</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1622015527303493</v>
+        <v>0.1641015527303493</v>
       </c>
       <c r="C45">
-        <v>53.82590914198943</v>
+        <v>29.44750607474396</v>
       </c>
       <c r="D45">
-        <v>706.9269091419894</v>
+        <v>697.945506074744</v>
       </c>
       <c r="E45">
-        <v>169.571</v>
+        <v>184.9680000000001</v>
       </c>
       <c r="F45">
-        <v>662.071</v>
+        <v>677.4680000000001</v>
       </c>
       <c r="G45">
         <v>8.970000000000001</v>
@@ -4977,37 +4977,37 @@
         <v>41</v>
       </c>
       <c r="M45">
-        <v>156.1163418</v>
+        <v>159.7469544</v>
       </c>
       <c r="N45">
-        <v>-115.1163418</v>
+        <v>-118.7469544</v>
       </c>
       <c r="O45">
-        <v>-25.325595196</v>
+        <v>-26.124329968</v>
       </c>
       <c r="P45">
-        <v>-89.79074660400002</v>
+        <v>-92.62262443200001</v>
       </c>
       <c r="Q45">
-        <v>-10.79074660400002</v>
+        <v>-13.62262443200001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1169576084415155</v>
+        <v>0.1182282800208283</v>
       </c>
       <c r="T45">
-        <v>1.643362781559251</v>
+        <v>1.672708545515666</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.05777742352914908</v>
+        <v>0.05646430026712296</v>
       </c>
       <c r="W45">
-        <v>0.2221760835318267</v>
+        <v>0.2224857179970124</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.262624652405223</v>
+        <v>0.2566559103051044</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1641015527303493</v>
+        <v>0.1660015527303493</v>
       </c>
       <c r="C46">
-        <v>29.44750607474396</v>
+        <v>5.2944547730267</v>
       </c>
       <c r="D46">
-        <v>697.945506074744</v>
+        <v>689.1894547730267</v>
       </c>
       <c r="E46">
-        <v>184.9680000000001</v>
+        <v>200.365</v>
       </c>
       <c r="F46">
-        <v>677.4680000000001</v>
+        <v>692.865</v>
       </c>
       <c r="G46">
         <v>8.970000000000001</v>
@@ -5059,37 +5059,37 @@
         <v>41</v>
       </c>
       <c r="M46">
-        <v>159.7469544</v>
+        <v>163.377567</v>
       </c>
       <c r="N46">
-        <v>-118.7469544</v>
+        <v>-122.377567</v>
       </c>
       <c r="O46">
-        <v>-26.124329968</v>
+        <v>-26.92306474</v>
       </c>
       <c r="P46">
-        <v>-92.62262443200001</v>
+        <v>-95.45450226</v>
       </c>
       <c r="Q46">
-        <v>-13.62262443200001</v>
+        <v>-16.45450226</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1182282800208283</v>
+        <v>0.1195451578393888</v>
       </c>
       <c r="T46">
-        <v>1.672708545515666</v>
+        <v>1.703121428161405</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05646430026712296</v>
+        <v>0.05520953803896468</v>
       </c>
       <c r="W46">
-        <v>0.2224857179970124</v>
+        <v>0.2227815909304121</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2566559103051044</v>
+        <v>0.2509524456316576</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1660015527303493</v>
+        <v>0.1679015527303493</v>
       </c>
       <c r="C47">
-        <v>5.2944547730267</v>
+        <v>-18.64162110646873</v>
       </c>
       <c r="D47">
-        <v>689.1894547730267</v>
+        <v>680.6503788935313</v>
       </c>
       <c r="E47">
-        <v>200.365</v>
+        <v>215.7620000000001</v>
       </c>
       <c r="F47">
-        <v>692.865</v>
+        <v>708.2620000000001</v>
       </c>
       <c r="G47">
         <v>8.970000000000001</v>
@@ -5141,37 +5141,37 @@
         <v>41</v>
       </c>
       <c r="M47">
-        <v>163.377567</v>
+        <v>167.0081796</v>
       </c>
       <c r="N47">
-        <v>-122.377567</v>
+        <v>-126.0081796</v>
       </c>
       <c r="O47">
-        <v>-26.92306474</v>
+        <v>-27.72179951200001</v>
       </c>
       <c r="P47">
-        <v>-95.45450226</v>
+        <v>-98.28638008800003</v>
       </c>
       <c r="Q47">
-        <v>-16.45450226</v>
+        <v>-19.28638008800003</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1195451578393888</v>
+        <v>0.1209108089104886</v>
       </c>
       <c r="T47">
-        <v>1.703121428161405</v>
+        <v>1.734660713868098</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05520953803896468</v>
+        <v>0.05400933069029152</v>
       </c>
       <c r="W47">
-        <v>0.2227815909304121</v>
+        <v>0.2230645998232293</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2509524456316576</v>
+        <v>0.2454969576831433</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1679015527303493</v>
+        <v>0.1698015527303493</v>
       </c>
       <c r="C48">
-        <v>-18.64162110646873</v>
+        <v>-42.36868785512752</v>
       </c>
       <c r="D48">
-        <v>680.6503788935313</v>
+        <v>672.3203121448726</v>
       </c>
       <c r="E48">
-        <v>215.7620000000001</v>
+        <v>231.1590000000001</v>
       </c>
       <c r="F48">
-        <v>708.2620000000001</v>
+        <v>723.6590000000001</v>
       </c>
       <c r="G48">
         <v>8.970000000000001</v>
@@ -5223,37 +5223,37 @@
         <v>41</v>
       </c>
       <c r="M48">
-        <v>167.0081796</v>
+        <v>170.6387922</v>
       </c>
       <c r="N48">
-        <v>-126.0081796</v>
+        <v>-129.6387922</v>
       </c>
       <c r="O48">
-        <v>-27.72179951200001</v>
+        <v>-28.52053428400001</v>
       </c>
       <c r="P48">
-        <v>-98.28638008800003</v>
+        <v>-101.118257916</v>
       </c>
       <c r="Q48">
-        <v>-19.28638008800003</v>
+        <v>-22.11825791600003</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1209108089104886</v>
+        <v>0.1223279939842714</v>
       </c>
       <c r="T48">
-        <v>1.734660713868098</v>
+        <v>1.767390161299571</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05400933069029152</v>
+        <v>0.0528601959947534</v>
       </c>
       <c r="W48">
-        <v>0.2230645998232293</v>
+        <v>0.2233355657844371</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2454969576831433</v>
+        <v>0.24027361815797</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1698015527303493</v>
+        <v>0.1717015527303493</v>
       </c>
       <c r="C49">
-        <v>-42.36868785512752</v>
+        <v>-65.89432650092488</v>
       </c>
       <c r="D49">
-        <v>672.3203121448726</v>
+        <v>664.1916734990751</v>
       </c>
       <c r="E49">
-        <v>231.1590000000001</v>
+        <v>246.556</v>
       </c>
       <c r="F49">
-        <v>723.6590000000001</v>
+        <v>739.056</v>
       </c>
       <c r="G49">
         <v>8.970000000000001</v>
@@ -5305,37 +5305,37 @@
         <v>41</v>
       </c>
       <c r="M49">
-        <v>170.6387922</v>
+        <v>174.2694048</v>
       </c>
       <c r="N49">
-        <v>-129.6387922</v>
+        <v>-133.2694048</v>
       </c>
       <c r="O49">
-        <v>-28.52053428400001</v>
+        <v>-29.319269056</v>
       </c>
       <c r="P49">
-        <v>-101.118257916</v>
+        <v>-103.950135744</v>
       </c>
       <c r="Q49">
-        <v>-22.11825791600003</v>
+        <v>-24.95013574400002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1223279939842714</v>
+        <v>0.1237996861762767</v>
       </c>
       <c r="T49">
-        <v>1.767390161299571</v>
+        <v>1.801378433632256</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0528601959947534</v>
+        <v>0.05175894191152938</v>
       </c>
       <c r="W49">
-        <v>0.2233355657844371</v>
+        <v>0.2235952414972614</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.24027361815797</v>
+        <v>0.235267917779679</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1717015527303493</v>
+        <v>0.1736015527303493</v>
       </c>
       <c r="C50">
-        <v>-65.89432650092488</v>
+        <v>-89.22575582019692</v>
       </c>
       <c r="D50">
-        <v>664.1916734990751</v>
+        <v>656.257244179803</v>
       </c>
       <c r="E50">
-        <v>246.556</v>
+        <v>261.953</v>
       </c>
       <c r="F50">
-        <v>739.056</v>
+        <v>754.453</v>
       </c>
       <c r="G50">
         <v>8.970000000000001</v>
@@ -5387,37 +5387,37 @@
         <v>41</v>
       </c>
       <c r="M50">
-        <v>174.2694048</v>
+        <v>177.9000174</v>
       </c>
       <c r="N50">
-        <v>-133.2694048</v>
+        <v>-136.9000174</v>
       </c>
       <c r="O50">
-        <v>-29.319269056</v>
+        <v>-30.118003828</v>
       </c>
       <c r="P50">
-        <v>-103.950135744</v>
+        <v>-106.782013572</v>
       </c>
       <c r="Q50">
-        <v>-24.95013574400002</v>
+        <v>-27.782013572</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1237996861762767</v>
+        <v>0.1253290917875762</v>
       </c>
       <c r="T50">
-        <v>1.801378433632255</v>
+        <v>1.836699579389751</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05175894191152938</v>
+        <v>0.0507026369745594</v>
       </c>
       <c r="W50">
-        <v>0.2235952414972614</v>
+        <v>0.2238443182013989</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.235267917779679</v>
+        <v>0.2304665317025427</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1736015527303493</v>
+        <v>0.1755015527303493</v>
       </c>
       <c r="C51">
-        <v>-89.22575582019692</v>
+        <v>-112.3698537194916</v>
       </c>
       <c r="D51">
-        <v>656.257244179803</v>
+        <v>648.5101462805084</v>
       </c>
       <c r="E51">
-        <v>261.953</v>
+        <v>277.35</v>
       </c>
       <c r="F51">
-        <v>754.453</v>
+        <v>769.85</v>
       </c>
       <c r="G51">
         <v>8.970000000000001</v>
@@ -5469,37 +5469,37 @@
         <v>41</v>
       </c>
       <c r="M51">
-        <v>177.9000174</v>
+        <v>181.53063</v>
       </c>
       <c r="N51">
-        <v>-136.9000174</v>
+        <v>-140.53063</v>
       </c>
       <c r="O51">
-        <v>-30.118003828</v>
+        <v>-30.9167386</v>
       </c>
       <c r="P51">
-        <v>-106.782013572</v>
+        <v>-109.6138914</v>
       </c>
       <c r="Q51">
-        <v>-27.782013572</v>
+        <v>-30.6138914</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1253290917875762</v>
+        <v>0.1269196736233277</v>
       </c>
       <c r="T51">
-        <v>1.836699579389751</v>
+        <v>1.873433570977546</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.0507026369745594</v>
+        <v>0.04968858423506821</v>
       </c>
       <c r="W51">
-        <v>0.2238443182013989</v>
+        <v>0.2240834318373709</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2304665317025427</v>
+        <v>0.2258572010684918</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1755015527303493</v>
+        <v>0.1774015527303494</v>
       </c>
       <c r="C52">
-        <v>-112.3698537194916</v>
+        <v>-135.3331771206156</v>
       </c>
       <c r="D52">
-        <v>648.5101462805084</v>
+        <v>640.9438228793845</v>
       </c>
       <c r="E52">
-        <v>277.35</v>
+        <v>292.7470000000001</v>
       </c>
       <c r="F52">
-        <v>769.85</v>
+        <v>785.2470000000001</v>
       </c>
       <c r="G52">
         <v>8.970000000000001</v>
@@ -5551,37 +5551,37 @@
         <v>41</v>
       </c>
       <c r="M52">
-        <v>181.53063</v>
+        <v>185.1612426</v>
       </c>
       <c r="N52">
-        <v>-140.53063</v>
+        <v>-144.1612426</v>
       </c>
       <c r="O52">
-        <v>-30.9167386</v>
+        <v>-31.71547337200001</v>
       </c>
       <c r="P52">
-        <v>-109.6138914</v>
+        <v>-112.445769228</v>
       </c>
       <c r="Q52">
-        <v>-30.6138914</v>
+        <v>-33.44576922800003</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1269196736233277</v>
+        <v>0.1285751771666609</v>
       </c>
       <c r="T52">
-        <v>1.873433570977546</v>
+        <v>1.911666909160761</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04968858423506821</v>
+        <v>0.0487142982696747</v>
       </c>
       <c r="W52">
-        <v>0.2240834318373709</v>
+        <v>0.2243131684680107</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2258572010684918</v>
+        <v>0.2214286284985214</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1774015527303494</v>
+        <v>0.1793015527303493</v>
       </c>
       <c r="C53">
-        <v>-135.3331771206156</v>
+        <v>-158.1219804697148</v>
       </c>
       <c r="D53">
-        <v>640.9438228793845</v>
+        <v>633.5520195302852</v>
       </c>
       <c r="E53">
-        <v>292.7470000000001</v>
+        <v>308.144</v>
       </c>
       <c r="F53">
-        <v>785.2470000000001</v>
+        <v>800.644</v>
       </c>
       <c r="G53">
         <v>8.970000000000001</v>
@@ -5633,37 +5633,37 @@
         <v>41</v>
       </c>
       <c r="M53">
-        <v>185.1612426</v>
+        <v>188.7918552</v>
       </c>
       <c r="N53">
-        <v>-144.1612426</v>
+        <v>-147.7918552</v>
       </c>
       <c r="O53">
-        <v>-31.71547337200001</v>
+        <v>-32.514208144</v>
       </c>
       <c r="P53">
-        <v>-112.445769228</v>
+        <v>-115.277647056</v>
       </c>
       <c r="Q53">
-        <v>-33.44576922800003</v>
+        <v>-36.27764705600001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1285751771666609</v>
+        <v>0.1302996600242997</v>
       </c>
       <c r="T53">
-        <v>1.911666909160761</v>
+        <v>1.95149330310161</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.0487142982696747</v>
+        <v>0.04777748484141174</v>
       </c>
       <c r="W53">
-        <v>0.2243131684680107</v>
+        <v>0.2245340690743951</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2214286284985214</v>
+        <v>0.2171703856427806</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1793015527303493</v>
+        <v>0.1812015527303493</v>
       </c>
       <c r="C54">
-        <v>-158.1219804697148</v>
+        <v>-180.7422329802014</v>
       </c>
       <c r="D54">
-        <v>633.5520195302852</v>
+        <v>626.3287670197986</v>
       </c>
       <c r="E54">
-        <v>308.144</v>
+        <v>323.5410000000001</v>
       </c>
       <c r="F54">
-        <v>800.644</v>
+        <v>816.0410000000001</v>
       </c>
       <c r="G54">
         <v>8.970000000000001</v>
@@ -5715,37 +5715,37 @@
         <v>41</v>
       </c>
       <c r="M54">
-        <v>188.7918552</v>
+        <v>192.4224678</v>
       </c>
       <c r="N54">
-        <v>-147.7918552</v>
+        <v>-151.4224678</v>
       </c>
       <c r="O54">
-        <v>-32.514208144</v>
+        <v>-33.312942916</v>
       </c>
       <c r="P54">
-        <v>-115.277647056</v>
+        <v>-118.109524884</v>
       </c>
       <c r="Q54">
-        <v>-36.27764705600001</v>
+        <v>-39.10952488400002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1302996600242997</v>
+        <v>0.1320975251311997</v>
       </c>
       <c r="T54">
-        <v>1.95149330310161</v>
+        <v>1.993014437210155</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04777748484141174</v>
+        <v>0.04687602286327189</v>
       </c>
       <c r="W54">
-        <v>0.2245340690743951</v>
+        <v>0.2247466338088405</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2171703856427806</v>
+        <v>0.2130728311966904</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1812015527303493</v>
+        <v>0.1831015527303493</v>
       </c>
       <c r="C55">
-        <v>-180.7422329802014</v>
+        <v>-203.199634709433</v>
       </c>
       <c r="D55">
-        <v>626.3287670197986</v>
+        <v>619.2683652905671</v>
       </c>
       <c r="E55">
-        <v>323.5410000000001</v>
+        <v>338.9380000000001</v>
       </c>
       <c r="F55">
-        <v>816.0410000000001</v>
+        <v>831.4380000000001</v>
       </c>
       <c r="G55">
         <v>8.970000000000001</v>
@@ -5797,37 +5797,37 @@
         <v>41</v>
       </c>
       <c r="M55">
-        <v>192.4224678</v>
+        <v>196.0530804</v>
       </c>
       <c r="N55">
-        <v>-151.4224678</v>
+        <v>-155.0530804</v>
       </c>
       <c r="O55">
-        <v>-33.312942916</v>
+        <v>-34.11167768800001</v>
       </c>
       <c r="P55">
-        <v>-118.109524884</v>
+        <v>-120.941402712</v>
       </c>
       <c r="Q55">
-        <v>-39.10952488400002</v>
+        <v>-41.94140271200001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1320975251311997</v>
+        <v>0.1339735582862258</v>
       </c>
       <c r="T55">
-        <v>1.993014437210155</v>
+        <v>2.036340838019072</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04687602286327189</v>
+        <v>0.04600794836580389</v>
       </c>
       <c r="W55">
-        <v>0.2247466338088405</v>
+        <v>0.2249513257753434</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2130728311966904</v>
+        <v>0.2091270380263813</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1831015527303493</v>
+        <v>0.1850015527303494</v>
       </c>
       <c r="C56">
-        <v>-203.199634709433</v>
+        <v>-225.4996315601553</v>
       </c>
       <c r="D56">
-        <v>619.2683652905671</v>
+        <v>612.3653684398448</v>
       </c>
       <c r="E56">
-        <v>338.9380000000001</v>
+        <v>354.3350000000002</v>
       </c>
       <c r="F56">
-        <v>831.4380000000001</v>
+        <v>846.8350000000002</v>
       </c>
       <c r="G56">
         <v>8.970000000000001</v>
@@ -5879,37 +5879,37 @@
         <v>41</v>
       </c>
       <c r="M56">
-        <v>196.0530804</v>
+        <v>199.683693</v>
       </c>
       <c r="N56">
-        <v>-155.0530804</v>
+        <v>-158.683693</v>
       </c>
       <c r="O56">
-        <v>-34.11167768800001</v>
+        <v>-34.91041246000001</v>
       </c>
       <c r="P56">
-        <v>-120.941402712</v>
+        <v>-123.77328054</v>
       </c>
       <c r="Q56">
-        <v>-41.94140271200001</v>
+        <v>-44.77328054000003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1339735582862258</v>
+        <v>0.1359329706925864</v>
       </c>
       <c r="T56">
-        <v>2.036340838019072</v>
+        <v>2.081592856641718</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04600794836580389</v>
+        <v>0.04517144021369836</v>
       </c>
       <c r="W56">
-        <v>0.2249513257753434</v>
+        <v>0.2251485743976099</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2091270380263813</v>
+        <v>0.2053247282440834</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1850015527303494</v>
+        <v>0.1869015527303493</v>
       </c>
       <c r="C57">
-        <v>-225.4996315601553</v>
+        <v>-247.6474292896715</v>
       </c>
       <c r="D57">
-        <v>612.3653684398448</v>
+        <v>605.6145707103285</v>
       </c>
       <c r="E57">
-        <v>354.3350000000002</v>
+        <v>369.7320000000001</v>
       </c>
       <c r="F57">
-        <v>846.8350000000002</v>
+        <v>862.2320000000001</v>
       </c>
       <c r="G57">
         <v>8.970000000000001</v>
@@ -5961,37 +5961,37 @@
         <v>41</v>
       </c>
       <c r="M57">
-        <v>199.683693</v>
+        <v>203.3143056</v>
       </c>
       <c r="N57">
-        <v>-158.683693</v>
+        <v>-162.3143056</v>
       </c>
       <c r="O57">
-        <v>-34.91041246000001</v>
+        <v>-35.70914723200001</v>
       </c>
       <c r="P57">
-        <v>-123.77328054</v>
+        <v>-126.605158368</v>
       </c>
       <c r="Q57">
-        <v>-44.77328054000003</v>
+        <v>-47.60515836800003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1359329706925864</v>
+        <v>0.1379814472992361</v>
       </c>
       <c r="T57">
-        <v>2.081592856641718</v>
+        <v>2.128901785201757</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04517144021369836</v>
+        <v>0.04436480735273946</v>
       </c>
       <c r="W57">
-        <v>0.2251485743976099</v>
+        <v>0.225338778426224</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2053247282440834</v>
+        <v>0.2016582152397248</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1869015527303493</v>
+        <v>0.1888015527303493</v>
       </c>
       <c r="C58">
-        <v>-247.6474292896715</v>
+        <v>-269.6480066024869</v>
       </c>
       <c r="D58">
-        <v>605.6145707103285</v>
+        <v>599.0109933975132</v>
       </c>
       <c r="E58">
-        <v>369.7320000000001</v>
+        <v>385.1290000000001</v>
       </c>
       <c r="F58">
-        <v>862.2320000000001</v>
+        <v>877.6290000000001</v>
       </c>
       <c r="G58">
         <v>8.970000000000001</v>
@@ -6043,37 +6043,37 @@
         <v>41</v>
       </c>
       <c r="M58">
-        <v>203.3143056</v>
+        <v>206.9449182</v>
       </c>
       <c r="N58">
-        <v>-162.3143056</v>
+        <v>-165.9449182</v>
       </c>
       <c r="O58">
-        <v>-35.70914723200001</v>
+        <v>-36.50788200400001</v>
       </c>
       <c r="P58">
-        <v>-126.605158368</v>
+        <v>-129.437036196</v>
       </c>
       <c r="Q58">
-        <v>-47.60515836800003</v>
+        <v>-50.43703619600004</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1379814472992361</v>
+        <v>0.1401252018875904</v>
       </c>
       <c r="T58">
-        <v>2.128901785201757</v>
+        <v>2.178411129043658</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04436480735273946</v>
+        <v>0.04358647739918263</v>
       </c>
       <c r="W58">
-        <v>0.225338778426224</v>
+        <v>0.2255223086292727</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2016582152397248</v>
+        <v>0.1981203518144665</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1888015527303493</v>
+        <v>0.1907015527303493</v>
       </c>
       <c r="C59">
-        <v>-269.6480066024869</v>
+        <v>-291.5061273956219</v>
       </c>
       <c r="D59">
-        <v>599.0109933975132</v>
+        <v>592.5498726043783</v>
       </c>
       <c r="E59">
-        <v>385.1290000000001</v>
+        <v>400.5260000000002</v>
       </c>
       <c r="F59">
-        <v>877.6290000000001</v>
+        <v>893.0260000000002</v>
       </c>
       <c r="G59">
         <v>8.970000000000001</v>
@@ -6125,37 +6125,37 @@
         <v>41</v>
       </c>
       <c r="M59">
-        <v>206.9449182</v>
+        <v>210.5755308000001</v>
       </c>
       <c r="N59">
-        <v>-165.9449182</v>
+        <v>-169.5755308000001</v>
       </c>
       <c r="O59">
-        <v>-36.50788200400001</v>
+        <v>-37.30661677600001</v>
       </c>
       <c r="P59">
-        <v>-129.437036196</v>
+        <v>-132.268914024</v>
       </c>
       <c r="Q59">
-        <v>-50.43703619600004</v>
+        <v>-53.26891402400003</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1401252018875904</v>
+        <v>0.1423710400277711</v>
       </c>
       <c r="T59">
-        <v>2.178411129043658</v>
+        <v>2.230278060687555</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04358647739918263</v>
+        <v>0.04283498640954155</v>
       </c>
       <c r="W59">
-        <v>0.2255223086292727</v>
+        <v>0.2256995102046301</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1981203518144665</v>
+        <v>0.1947044836797344</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1907015527303493</v>
+        <v>0.1926015527303493</v>
       </c>
       <c r="C60">
-        <v>-291.5061273956217</v>
+        <v>-313.2263522198917</v>
       </c>
       <c r="D60">
-        <v>592.5498726043783</v>
+        <v>586.2266477801082</v>
       </c>
       <c r="E60">
-        <v>400.526</v>
+        <v>415.923</v>
       </c>
       <c r="F60">
-        <v>893.026</v>
+        <v>908.423</v>
       </c>
       <c r="G60">
         <v>8.970000000000001</v>
@@ -6207,37 +6207,37 @@
         <v>41</v>
       </c>
       <c r="M60">
-        <v>210.5755308</v>
+        <v>214.2061434</v>
       </c>
       <c r="N60">
-        <v>-169.5755308</v>
+        <v>-173.2061434</v>
       </c>
       <c r="O60">
-        <v>-37.306616776</v>
+        <v>-38.105351548</v>
       </c>
       <c r="P60">
-        <v>-132.268914024</v>
+        <v>-135.100791852</v>
       </c>
       <c r="Q60">
-        <v>-53.268914024</v>
+        <v>-56.10079185199999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1423710400277711</v>
+        <v>0.1447264312479606</v>
       </c>
       <c r="T60">
-        <v>2.230278060687554</v>
+        <v>2.284675086557982</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04283498640954156</v>
+        <v>0.04210896969073577</v>
       </c>
       <c r="W60">
-        <v>0.2256995102046301</v>
+        <v>0.2258707049469245</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1947044836797344</v>
+        <v>0.1914044076851625</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1926015527303493</v>
+        <v>0.1945015527303493</v>
       </c>
       <c r="C61">
-        <v>-313.2263522198917</v>
+        <v>-334.813049015102</v>
       </c>
       <c r="D61">
-        <v>586.2266477801082</v>
+        <v>580.0369509848979</v>
       </c>
       <c r="E61">
-        <v>415.923</v>
+        <v>431.3199999999999</v>
       </c>
       <c r="F61">
-        <v>908.423</v>
+        <v>923.8199999999999</v>
       </c>
       <c r="G61">
         <v>8.970000000000001</v>
@@ -6289,37 +6289,37 @@
         <v>41</v>
       </c>
       <c r="M61">
-        <v>214.2061434</v>
+        <v>217.836756</v>
       </c>
       <c r="N61">
-        <v>-173.2061434</v>
+        <v>-176.836756</v>
       </c>
       <c r="O61">
-        <v>-38.105351548</v>
+        <v>-38.90408632</v>
       </c>
       <c r="P61">
-        <v>-135.100791852</v>
+        <v>-137.93266968</v>
       </c>
       <c r="Q61">
-        <v>-56.10079185199999</v>
+        <v>-58.93266967999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1447264312479606</v>
+        <v>0.1471995920291596</v>
       </c>
       <c r="T61">
-        <v>2.284675086557982</v>
+        <v>2.341791963721932</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04210896969073577</v>
+        <v>0.04140715352922351</v>
       </c>
       <c r="W61">
-        <v>0.2258707049469245</v>
+        <v>0.2260361931978091</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1914044076851625</v>
+        <v>0.1882143342237432</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1945015527303493</v>
+        <v>0.1964015527303493</v>
       </c>
       <c r="C62">
-        <v>-334.813049015102</v>
+        <v>-356.2704031722591</v>
       </c>
       <c r="D62">
-        <v>580.0369509848979</v>
+        <v>573.9765968277409</v>
       </c>
       <c r="E62">
-        <v>431.3199999999999</v>
+        <v>446.717</v>
       </c>
       <c r="F62">
-        <v>923.8199999999999</v>
+        <v>939.217</v>
       </c>
       <c r="G62">
         <v>8.970000000000001</v>
@@ -6371,37 +6371,37 @@
         <v>41</v>
       </c>
       <c r="M62">
-        <v>217.836756</v>
+        <v>221.4673686</v>
       </c>
       <c r="N62">
-        <v>-176.836756</v>
+        <v>-180.4673686</v>
       </c>
       <c r="O62">
-        <v>-38.90408632</v>
+        <v>-39.702821092</v>
       </c>
       <c r="P62">
-        <v>-137.93266968</v>
+        <v>-140.764547508</v>
       </c>
       <c r="Q62">
-        <v>-58.93266967999998</v>
+        <v>-61.76454750800002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1471995920291596</v>
+        <v>0.1497995815683689</v>
       </c>
       <c r="T62">
-        <v>2.341791963721932</v>
+        <v>2.401837911509674</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04140715352922351</v>
+        <v>0.04072834773366246</v>
       </c>
       <c r="W62">
-        <v>0.2260361931978091</v>
+        <v>0.2261962556044024</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1882143342237432</v>
+        <v>0.1851288533348294</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1964015527303493</v>
+        <v>0.1983015527303493</v>
       </c>
       <c r="C63">
-        <v>-356.2704031722591</v>
+        <v>-377.6024269715116</v>
       </c>
       <c r="D63">
-        <v>573.9765968277409</v>
+        <v>568.0415730284884</v>
       </c>
       <c r="E63">
-        <v>446.717</v>
+        <v>462.114</v>
       </c>
       <c r="F63">
-        <v>939.217</v>
+        <v>954.614</v>
       </c>
       <c r="G63">
         <v>8.970000000000001</v>
@@ -6453,37 +6453,37 @@
         <v>41</v>
       </c>
       <c r="M63">
-        <v>221.4673686</v>
+        <v>225.0979812</v>
       </c>
       <c r="N63">
-        <v>-180.4673686</v>
+        <v>-184.0979812</v>
       </c>
       <c r="O63">
-        <v>-39.702821092</v>
+        <v>-40.501555864</v>
       </c>
       <c r="P63">
-        <v>-140.764547508</v>
+        <v>-143.596425336</v>
       </c>
       <c r="Q63">
-        <v>-61.76454750800002</v>
+        <v>-64.59642533600001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1497995815683689</v>
+        <v>0.1525364126622733</v>
       </c>
       <c r="T63">
-        <v>2.401837911509674</v>
+        <v>2.465044172338876</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04072834773366246</v>
+        <v>0.04007143889924855</v>
       </c>
       <c r="W63">
-        <v>0.2261962556044024</v>
+        <v>0.2263511547075572</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1851288533348294</v>
+        <v>0.1821429040874935</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1983015527303493</v>
+        <v>0.2002015527303493</v>
       </c>
       <c r="C64">
-        <v>-377.6024269715116</v>
+        <v>-398.8129684405442</v>
       </c>
       <c r="D64">
-        <v>568.0415730284884</v>
+        <v>562.2280315594559</v>
       </c>
       <c r="E64">
-        <v>462.114</v>
+        <v>477.5110000000001</v>
       </c>
       <c r="F64">
-        <v>954.614</v>
+        <v>970.0110000000001</v>
       </c>
       <c r="G64">
         <v>8.970000000000001</v>
@@ -6535,37 +6535,37 @@
         <v>41</v>
       </c>
       <c r="M64">
-        <v>225.0979812</v>
+        <v>228.7285938</v>
       </c>
       <c r="N64">
-        <v>-184.0979812</v>
+        <v>-187.7285938</v>
       </c>
       <c r="O64">
-        <v>-40.501555864</v>
+        <v>-41.30029063600001</v>
       </c>
       <c r="P64">
-        <v>-143.596425336</v>
+        <v>-146.428303164</v>
       </c>
       <c r="Q64">
-        <v>-64.59642533600001</v>
+        <v>-67.42830316400003</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1525364126622733</v>
+        <v>0.1554211805720645</v>
       </c>
       <c r="T64">
-        <v>2.465044172338876</v>
+        <v>2.531666987807494</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04007143889924855</v>
+        <v>0.03943538431354619</v>
       </c>
       <c r="W64">
-        <v>0.2263511547075572</v>
+        <v>0.2265011363788658</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1821429040874935</v>
+        <v>0.1792517468797554</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2002015527303493</v>
+        <v>0.2021015527303494</v>
       </c>
       <c r="C65">
-        <v>-398.8129684405442</v>
+        <v>-419.9057196745215</v>
       </c>
       <c r="D65">
-        <v>562.2280315594559</v>
+        <v>556.5322803254785</v>
       </c>
       <c r="E65">
-        <v>477.5110000000001</v>
+        <v>492.908</v>
       </c>
       <c r="F65">
-        <v>970.0110000000001</v>
+        <v>985.408</v>
       </c>
       <c r="G65">
         <v>8.970000000000001</v>
@@ -6617,37 +6617,37 @@
         <v>41</v>
       </c>
       <c r="M65">
-        <v>228.7285938</v>
+        <v>232.3592064</v>
       </c>
       <c r="N65">
-        <v>-187.7285938</v>
+        <v>-191.3592064</v>
       </c>
       <c r="O65">
-        <v>-41.30029063600001</v>
+        <v>-42.099025408</v>
       </c>
       <c r="P65">
-        <v>-146.428303164</v>
+        <v>-149.260180992</v>
       </c>
       <c r="Q65">
-        <v>-67.42830316400003</v>
+        <v>-70.26018099200002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1554211805720645</v>
+        <v>0.1584662133657329</v>
       </c>
       <c r="T65">
-        <v>2.531666987807494</v>
+        <v>2.601991070802147</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03943538431354619</v>
+        <v>0.03881920643364704</v>
       </c>
       <c r="W65">
-        <v>0.2265011363788658</v>
+        <v>0.2266464311229461</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1792517468797554</v>
+        <v>0.1764509383347592</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2021015527303494</v>
+        <v>0.2040015527303493</v>
       </c>
       <c r="C66">
-        <v>-419.9057196745215</v>
+        <v>-440.8842246553842</v>
       </c>
       <c r="D66">
-        <v>556.5322803254785</v>
+        <v>550.9507753446159</v>
       </c>
       <c r="E66">
-        <v>492.908</v>
+        <v>508.3050000000001</v>
       </c>
       <c r="F66">
-        <v>985.408</v>
+        <v>1000.805</v>
       </c>
       <c r="G66">
         <v>8.970000000000001</v>
@@ -6699,37 +6699,37 @@
         <v>41</v>
       </c>
       <c r="M66">
-        <v>232.3592064</v>
+        <v>235.989819</v>
       </c>
       <c r="N66">
-        <v>-191.3592064</v>
+        <v>-194.989819</v>
       </c>
       <c r="O66">
-        <v>-42.099025408</v>
+        <v>-42.89776018000001</v>
       </c>
       <c r="P66">
-        <v>-149.260180992</v>
+        <v>-152.09205882</v>
       </c>
       <c r="Q66">
-        <v>-70.26018099200002</v>
+        <v>-73.09205882000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1584662133657329</v>
+        <v>0.1616852480333253</v>
       </c>
       <c r="T66">
-        <v>2.601991070802147</v>
+        <v>2.676333672825066</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03881920643364704</v>
+        <v>0.03822198787312939</v>
       </c>
       <c r="W66">
-        <v>0.2266464311229461</v>
+        <v>0.2267872552595161</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1764509383347592</v>
+        <v>0.1737363085142245</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2040015527303493</v>
+        <v>0.2059015527303494</v>
       </c>
       <c r="C67">
-        <v>-440.8842246553842</v>
+        <v>-461.7518866052962</v>
       </c>
       <c r="D67">
-        <v>550.9507753446159</v>
+        <v>545.4801133947038</v>
       </c>
       <c r="E67">
-        <v>508.3050000000001</v>
+        <v>523.7020000000001</v>
       </c>
       <c r="F67">
-        <v>1000.805</v>
+        <v>1016.202</v>
       </c>
       <c r="G67">
         <v>8.970000000000001</v>
@@ -6781,37 +6781,37 @@
         <v>41</v>
       </c>
       <c r="M67">
-        <v>235.989819</v>
+        <v>239.6204316</v>
       </c>
       <c r="N67">
-        <v>-194.989819</v>
+        <v>-198.6204316</v>
       </c>
       <c r="O67">
-        <v>-42.89776018000001</v>
+        <v>-43.69649495200001</v>
       </c>
       <c r="P67">
-        <v>-152.09205882</v>
+        <v>-154.9239366480001</v>
       </c>
       <c r="Q67">
-        <v>-73.09205882000001</v>
+        <v>-75.92393664800005</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1616852480333253</v>
+        <v>0.1650936376813643</v>
       </c>
       <c r="T67">
-        <v>2.676333672825066</v>
+        <v>2.755049369084626</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03822198787312939</v>
+        <v>0.03764286684474864</v>
       </c>
       <c r="W67">
-        <v>0.2267872552595161</v>
+        <v>0.2269238119980083</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1737363085142245</v>
+        <v>0.1711039402034029</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2059015527303494</v>
+        <v>0.2078015527303493</v>
       </c>
       <c r="C68">
-        <v>-461.7518866052962</v>
+        <v>-482.5119749062999</v>
       </c>
       <c r="D68">
-        <v>545.4801133947038</v>
+        <v>540.1170250937002</v>
       </c>
       <c r="E68">
-        <v>523.7020000000001</v>
+        <v>539.0990000000002</v>
       </c>
       <c r="F68">
-        <v>1016.202</v>
+        <v>1031.599</v>
       </c>
       <c r="G68">
         <v>8.970000000000001</v>
@@ -6863,37 +6863,37 @@
         <v>41</v>
       </c>
       <c r="M68">
-        <v>239.6204316</v>
+        <v>243.2510442000001</v>
       </c>
       <c r="N68">
-        <v>-198.6204316</v>
+        <v>-202.2510442000001</v>
       </c>
       <c r="O68">
-        <v>-43.69649495200001</v>
+        <v>-44.49522972400001</v>
       </c>
       <c r="P68">
-        <v>-154.9239366480001</v>
+        <v>-157.755814476</v>
       </c>
       <c r="Q68">
-        <v>-75.92393664800005</v>
+        <v>-78.75581447600004</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1650936376813643</v>
+        <v>0.1687085963989814</v>
       </c>
       <c r="T68">
-        <v>2.755049369084626</v>
+        <v>2.838535713602342</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03764286684474864</v>
+        <v>0.03708103301124492</v>
       </c>
       <c r="W68">
-        <v>0.2269238119980083</v>
+        <v>0.2270562924159485</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1711039402034029</v>
+        <v>0.1685501500511133</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2078015527303493</v>
+        <v>0.2097015527303493</v>
       </c>
       <c r="C69">
-        <v>-482.5119749062999</v>
+        <v>-503.1676316157516</v>
       </c>
       <c r="D69">
-        <v>540.1170250937002</v>
+        <v>534.8583683842485</v>
       </c>
       <c r="E69">
-        <v>539.0990000000002</v>
+        <v>554.4960000000001</v>
       </c>
       <c r="F69">
-        <v>1031.599</v>
+        <v>1046.996</v>
       </c>
       <c r="G69">
         <v>8.970000000000001</v>
@@ -6945,37 +6945,37 @@
         <v>41</v>
       </c>
       <c r="M69">
-        <v>243.2510442000001</v>
+        <v>246.8816568</v>
       </c>
       <c r="N69">
-        <v>-202.2510442000001</v>
+        <v>-205.8816568</v>
       </c>
       <c r="O69">
-        <v>-44.49522972400001</v>
+        <v>-45.29396449600001</v>
       </c>
       <c r="P69">
-        <v>-157.755814476</v>
+        <v>-160.587692304</v>
       </c>
       <c r="Q69">
-        <v>-78.75581447600004</v>
+        <v>-81.58769230400003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1687085963989814</v>
+        <v>0.1725494900364496</v>
       </c>
       <c r="T69">
-        <v>2.838535713602342</v>
+        <v>2.927239954652415</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03708103301124492</v>
+        <v>0.03653572370225603</v>
       </c>
       <c r="W69">
-        <v>0.2270562924159485</v>
+        <v>0.227184876351008</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1685501500511133</v>
+        <v>0.166071471373891</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2097015527303493</v>
+        <v>0.2116015527303494</v>
       </c>
       <c r="C70">
-        <v>-503.1676316157516</v>
+        <v>-523.7218776048114</v>
       </c>
       <c r="D70">
-        <v>534.8583683842485</v>
+        <v>529.7011223951886</v>
       </c>
       <c r="E70">
-        <v>554.4960000000001</v>
+        <v>569.893</v>
       </c>
       <c r="F70">
-        <v>1046.996</v>
+        <v>1062.393</v>
       </c>
       <c r="G70">
         <v>8.970000000000001</v>
@@ -7027,37 +7027,37 @@
         <v>41</v>
       </c>
       <c r="M70">
-        <v>246.8816568</v>
+        <v>250.5122694</v>
       </c>
       <c r="N70">
-        <v>-205.8816568</v>
+        <v>-209.5122694</v>
       </c>
       <c r="O70">
-        <v>-45.29396449600001</v>
+        <v>-46.092699268</v>
       </c>
       <c r="P70">
-        <v>-160.587692304</v>
+        <v>-163.419570132</v>
       </c>
       <c r="Q70">
-        <v>-81.58769230400003</v>
+        <v>-84.41957013199999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1725494900364496</v>
+        <v>0.1766381832634319</v>
       </c>
       <c r="T70">
-        <v>2.927239954652415</v>
+        <v>3.021667049963784</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03653572370225603</v>
+        <v>0.03600622046019435</v>
       </c>
       <c r="W70">
-        <v>0.227184876351008</v>
+        <v>0.2273097332154862</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.166071471373891</v>
+        <v>0.1636646384554289</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2116015527303494</v>
+        <v>0.2135015527303493</v>
       </c>
       <c r="C71">
-        <v>-523.7218776048114</v>
+        <v>-544.1776183451942</v>
       </c>
       <c r="D71">
-        <v>529.7011223951886</v>
+        <v>524.6423816548059</v>
       </c>
       <c r="E71">
-        <v>569.893</v>
+        <v>585.2900000000002</v>
       </c>
       <c r="F71">
-        <v>1062.393</v>
+        <v>1077.79</v>
       </c>
       <c r="G71">
         <v>8.970000000000001</v>
@@ -7109,37 +7109,37 @@
         <v>41</v>
       </c>
       <c r="M71">
-        <v>250.5122694</v>
+        <v>254.142882</v>
       </c>
       <c r="N71">
-        <v>-209.5122694</v>
+        <v>-213.142882</v>
       </c>
       <c r="O71">
-        <v>-46.092699268</v>
+        <v>-46.89143404000001</v>
       </c>
       <c r="P71">
-        <v>-163.419570132</v>
+        <v>-166.25144796</v>
       </c>
       <c r="Q71">
-        <v>-84.41957013199999</v>
+        <v>-87.25144796000004</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1766381832634319</v>
+        <v>0.1809994560388796</v>
       </c>
       <c r="T71">
-        <v>3.021667049963784</v>
+        <v>3.122389284962577</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03600622046019435</v>
+        <v>0.03549184588219157</v>
       </c>
       <c r="W71">
-        <v>0.2273097332154862</v>
+        <v>0.2274310227409792</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1636646384554289</v>
+        <v>0.1613265721917798</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2135015527303493</v>
+        <v>0.2154015527303493</v>
       </c>
       <c r="C72">
-        <v>-544.1776183451942</v>
+        <v>-564.537649367468</v>
       </c>
       <c r="D72">
-        <v>524.6423816548059</v>
+        <v>519.6793506325321</v>
       </c>
       <c r="E72">
-        <v>585.2900000000002</v>
+        <v>600.6870000000001</v>
       </c>
       <c r="F72">
-        <v>1077.79</v>
+        <v>1093.187</v>
       </c>
       <c r="G72">
         <v>8.970000000000001</v>
@@ -7191,37 +7191,37 @@
         <v>41</v>
       </c>
       <c r="M72">
-        <v>254.142882</v>
+        <v>257.7734946</v>
       </c>
       <c r="N72">
-        <v>-213.142882</v>
+        <v>-216.7734946</v>
       </c>
       <c r="O72">
-        <v>-46.89143404000001</v>
+        <v>-47.69016881200001</v>
       </c>
       <c r="P72">
-        <v>-166.25144796</v>
+        <v>-169.083325788</v>
       </c>
       <c r="Q72">
-        <v>-87.25144796000004</v>
+        <v>-90.08332578800002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1809994560388796</v>
+        <v>0.1856615062471168</v>
       </c>
       <c r="T72">
-        <v>3.122389284962577</v>
+        <v>3.230057880995769</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03549184588219157</v>
+        <v>0.03499196072892127</v>
       </c>
       <c r="W72">
-        <v>0.2274310227409792</v>
+        <v>0.2275488956601204</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1613265721917798</v>
+        <v>0.1590543669496421</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2154015527303493</v>
+        <v>0.2173015527303493</v>
       </c>
       <c r="C73">
-        <v>-564.5376493674678</v>
+        <v>-584.8046614124484</v>
       </c>
       <c r="D73">
-        <v>519.6793506325321</v>
+        <v>514.8093385875517</v>
       </c>
       <c r="E73">
-        <v>600.6869999999999</v>
+        <v>616.0840000000001</v>
       </c>
       <c r="F73">
-        <v>1093.187</v>
+        <v>1108.584</v>
       </c>
       <c r="G73">
         <v>8.970000000000001</v>
@@ -7273,37 +7273,37 @@
         <v>41</v>
       </c>
       <c r="M73">
-        <v>257.7734946</v>
+        <v>261.4041072</v>
       </c>
       <c r="N73">
-        <v>-216.7734946</v>
+        <v>-220.4041072</v>
       </c>
       <c r="O73">
-        <v>-47.690168812</v>
+        <v>-48.488903584</v>
       </c>
       <c r="P73">
-        <v>-169.083325788</v>
+        <v>-171.915203616</v>
       </c>
       <c r="Q73">
-        <v>-90.083325788</v>
+        <v>-92.91520361599999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1856615062471167</v>
+        <v>0.1906565600416567</v>
       </c>
       <c r="T73">
-        <v>3.230057880995768</v>
+        <v>3.345417091031332</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03499196072892127</v>
+        <v>0.03450596127435292</v>
       </c>
       <c r="W73">
-        <v>0.2275488956601204</v>
+        <v>0.2276634943315076</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1590543669496421</v>
+        <v>0.156845278519786</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2173015527303493</v>
+        <v>0.2192015527303494</v>
       </c>
       <c r="C74">
-        <v>-584.8046614124484</v>
+        <v>-604.9812452956365</v>
       </c>
       <c r="D74">
-        <v>514.8093385875517</v>
+        <v>510.0297547043635</v>
       </c>
       <c r="E74">
-        <v>616.0840000000001</v>
+        <v>631.481</v>
       </c>
       <c r="F74">
-        <v>1108.584</v>
+        <v>1123.981</v>
       </c>
       <c r="G74">
         <v>8.970000000000001</v>
@@ -7355,37 +7355,37 @@
         <v>41</v>
       </c>
       <c r="M74">
-        <v>261.4041072</v>
+        <v>265.0347198</v>
       </c>
       <c r="N74">
-        <v>-220.4041072</v>
+        <v>-224.0347198</v>
       </c>
       <c r="O74">
-        <v>-48.488903584</v>
+        <v>-49.287638356</v>
       </c>
       <c r="P74">
-        <v>-171.915203616</v>
+        <v>-174.747081444</v>
       </c>
       <c r="Q74">
-        <v>-92.91520361599999</v>
+        <v>-95.747081444</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1906565600416567</v>
+        <v>0.1960216178209773</v>
       </c>
       <c r="T74">
-        <v>3.345417091031332</v>
+        <v>3.469321427736196</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03450596127435292</v>
+        <v>0.03403327687333439</v>
       </c>
       <c r="W74">
-        <v>0.2276634943315076</v>
+        <v>0.2277749533132678</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.156845278519786</v>
+        <v>0.1546967130606108</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2192015527303494</v>
+        <v>0.2211015527303493</v>
       </c>
       <c r="C75">
-        <v>-604.9812452956365</v>
+        <v>-625.0698965031703</v>
       </c>
       <c r="D75">
-        <v>510.0297547043635</v>
+        <v>505.3381034968297</v>
       </c>
       <c r="E75">
-        <v>631.481</v>
+        <v>646.8779999999999</v>
       </c>
       <c r="F75">
-        <v>1123.981</v>
+        <v>1139.378</v>
       </c>
       <c r="G75">
         <v>8.970000000000001</v>
@@ -7437,37 +7437,37 @@
         <v>41</v>
       </c>
       <c r="M75">
-        <v>265.0347198</v>
+        <v>268.6653324</v>
       </c>
       <c r="N75">
-        <v>-224.0347198</v>
+        <v>-227.6653324</v>
       </c>
       <c r="O75">
-        <v>-49.287638356</v>
+        <v>-50.08637312800001</v>
       </c>
       <c r="P75">
-        <v>-174.747081444</v>
+        <v>-177.578959272</v>
       </c>
       <c r="Q75">
-        <v>-95.747081444</v>
+        <v>-98.57895927200002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1960216178209773</v>
+        <v>0.2017993723525533</v>
       </c>
       <c r="T75">
-        <v>3.469321427736196</v>
+        <v>3.602756867264511</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03403327687333439</v>
+        <v>0.03357336772639744</v>
       </c>
       <c r="W75">
-        <v>0.2277749533132678</v>
+        <v>0.2278833998901155</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1546967130606108</v>
+        <v>0.1526062169381701</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2211015527303493</v>
+        <v>0.2230015527303493</v>
       </c>
       <c r="C76">
-        <v>-625.0698965031703</v>
+        <v>-645.0730195364329</v>
       </c>
       <c r="D76">
-        <v>505.3381034968297</v>
+        <v>500.7319804635671</v>
       </c>
       <c r="E76">
-        <v>646.8779999999999</v>
+        <v>662.2750000000001</v>
       </c>
       <c r="F76">
-        <v>1139.378</v>
+        <v>1154.775</v>
       </c>
       <c r="G76">
         <v>8.970000000000001</v>
@@ -7519,37 +7519,37 @@
         <v>41</v>
       </c>
       <c r="M76">
-        <v>268.6653324</v>
+        <v>272.295945</v>
       </c>
       <c r="N76">
-        <v>-227.6653324</v>
+        <v>-231.295945</v>
       </c>
       <c r="O76">
-        <v>-50.08637312800001</v>
+        <v>-50.8851079</v>
       </c>
       <c r="P76">
-        <v>-177.578959272</v>
+        <v>-180.4108371</v>
       </c>
       <c r="Q76">
-        <v>-98.57895927200002</v>
+        <v>-101.4108371</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2017993723525533</v>
+        <v>0.2080393472466555</v>
       </c>
       <c r="T76">
-        <v>3.602756867264511</v>
+        <v>3.746867141955092</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03357336772639744</v>
+        <v>0.03312572282337881</v>
       </c>
       <c r="W76">
-        <v>0.2278833998901155</v>
+        <v>0.2279889545582473</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1526062169381701</v>
+        <v>0.1505714673789945</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2230015527303493</v>
+        <v>0.2249015527303493</v>
       </c>
       <c r="C77">
-        <v>-645.0730195364329</v>
+        <v>-664.9929320211928</v>
       </c>
       <c r="D77">
-        <v>500.7319804635671</v>
+        <v>496.2090679788072</v>
       </c>
       <c r="E77">
-        <v>662.2750000000001</v>
+        <v>677.672</v>
       </c>
       <c r="F77">
-        <v>1154.775</v>
+        <v>1170.172</v>
       </c>
       <c r="G77">
         <v>8.970000000000001</v>
@@ -7601,37 +7601,37 @@
         <v>41</v>
       </c>
       <c r="M77">
-        <v>272.295945</v>
+        <v>275.9265576</v>
       </c>
       <c r="N77">
-        <v>-231.295945</v>
+        <v>-234.9265576</v>
       </c>
       <c r="O77">
-        <v>-50.8851079</v>
+        <v>-51.683842672</v>
       </c>
       <c r="P77">
-        <v>-180.4108371</v>
+        <v>-183.242714928</v>
       </c>
       <c r="Q77">
-        <v>-101.4108371</v>
+        <v>-104.242714928</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2080393472466555</v>
+        <v>0.2147993200485995</v>
       </c>
       <c r="T77">
-        <v>3.746867141955092</v>
+        <v>3.902986606203221</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03312572282337881</v>
+        <v>0.03268985804938698</v>
       </c>
       <c r="W77">
-        <v>0.2279889545582473</v>
+        <v>0.2280917314719546</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1505714673789945</v>
+        <v>0.1485902638608499</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2249015527303493</v>
+        <v>0.2268015527303494</v>
       </c>
       <c r="C78">
-        <v>-664.9929320211928</v>
+        <v>-684.8318685960496</v>
       </c>
       <c r="D78">
-        <v>496.2090679788072</v>
+        <v>491.7671314039503</v>
       </c>
       <c r="E78">
-        <v>677.672</v>
+        <v>693.069</v>
       </c>
       <c r="F78">
-        <v>1170.172</v>
+        <v>1185.569</v>
       </c>
       <c r="G78">
         <v>8.970000000000001</v>
@@ -7683,37 +7683,37 @@
         <v>41</v>
       </c>
       <c r="M78">
-        <v>275.9265576</v>
+        <v>279.5571702</v>
       </c>
       <c r="N78">
-        <v>-234.9265576</v>
+        <v>-238.5571702</v>
       </c>
       <c r="O78">
-        <v>-51.683842672</v>
+        <v>-52.48257744400001</v>
       </c>
       <c r="P78">
-        <v>-183.242714928</v>
+        <v>-186.074592756</v>
       </c>
       <c r="Q78">
-        <v>-104.242714928</v>
+        <v>-107.074592756</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2147993200485995</v>
+        <v>0.2221471165724516</v>
       </c>
       <c r="T78">
-        <v>3.902986606203221</v>
+        <v>4.072681676038143</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03268985804938698</v>
+        <v>0.03226531443835597</v>
       </c>
       <c r="W78">
-        <v>0.2280917314719546</v>
+        <v>0.2281918388554357</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1485902638608499</v>
+        <v>0.1466605201743454</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2268015527303494</v>
+        <v>0.2287015527303493</v>
       </c>
       <c r="C79">
-        <v>-684.8318685960496</v>
+        <v>-704.5919845938752</v>
       </c>
       <c r="D79">
-        <v>491.7671314039503</v>
+        <v>487.4040154061249</v>
       </c>
       <c r="E79">
-        <v>693.069</v>
+        <v>708.4660000000001</v>
       </c>
       <c r="F79">
-        <v>1185.569</v>
+        <v>1200.966</v>
       </c>
       <c r="G79">
         <v>8.970000000000001</v>
@@ -7765,37 +7765,37 @@
         <v>41</v>
       </c>
       <c r="M79">
-        <v>279.5571702</v>
+        <v>283.1877828</v>
       </c>
       <c r="N79">
-        <v>-238.5571702</v>
+        <v>-242.1877828</v>
       </c>
       <c r="O79">
-        <v>-52.48257744400001</v>
+        <v>-53.28131221600001</v>
       </c>
       <c r="P79">
-        <v>-186.074592756</v>
+        <v>-188.906470584</v>
       </c>
       <c r="Q79">
-        <v>-107.074592756</v>
+        <v>-109.906470584</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2221471165724516</v>
+        <v>0.2301628945984721</v>
       </c>
       <c r="T79">
-        <v>4.072681676038143</v>
+        <v>4.257803570403514</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03226531443835597</v>
+        <v>0.03185165656094115</v>
       </c>
       <c r="W79">
-        <v>0.2281918388554357</v>
+        <v>0.2282893793829301</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1466605201743454</v>
+        <v>0.144780257095187</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2287015527303493</v>
+        <v>0.2306015527303493</v>
       </c>
       <c r="C80">
-        <v>-704.5919845938752</v>
+        <v>-724.2753595290054</v>
       </c>
       <c r="D80">
-        <v>487.4040154061249</v>
+        <v>483.1176404709946</v>
       </c>
       <c r="E80">
-        <v>708.4660000000001</v>
+        <v>723.8630000000001</v>
       </c>
       <c r="F80">
-        <v>1200.966</v>
+        <v>1216.363</v>
       </c>
       <c r="G80">
         <v>8.970000000000001</v>
@@ -7847,37 +7847,37 @@
         <v>41</v>
       </c>
       <c r="M80">
-        <v>283.1877828</v>
+        <v>286.8183954</v>
       </c>
       <c r="N80">
-        <v>-242.1877828</v>
+        <v>-245.8183954</v>
       </c>
       <c r="O80">
-        <v>-53.28131221600001</v>
+        <v>-54.08004698800001</v>
       </c>
       <c r="P80">
-        <v>-188.906470584</v>
+        <v>-191.7383484120001</v>
       </c>
       <c r="Q80">
-        <v>-109.906470584</v>
+        <v>-112.7383484120001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2301628945984721</v>
+        <v>0.2389420800555422</v>
       </c>
       <c r="T80">
-        <v>4.257803570403514</v>
+        <v>4.460556121375109</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03185165656094115</v>
+        <v>0.03144847103485329</v>
       </c>
       <c r="W80">
-        <v>0.2282893793829301</v>
+        <v>0.2283844505299816</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.144780257095187</v>
+        <v>0.1429475956129695</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2306015527303493</v>
+        <v>0.2325015527303493</v>
       </c>
       <c r="C81">
-        <v>-724.2753595290054</v>
+        <v>-743.8840004020292</v>
       </c>
       <c r="D81">
-        <v>483.1176404709946</v>
+        <v>478.9059995979711</v>
       </c>
       <c r="E81">
-        <v>723.8630000000001</v>
+        <v>739.2600000000002</v>
       </c>
       <c r="F81">
-        <v>1216.363</v>
+        <v>1231.76</v>
       </c>
       <c r="G81">
         <v>8.970000000000001</v>
@@ -7929,37 +7929,37 @@
         <v>41</v>
       </c>
       <c r="M81">
-        <v>286.8183954</v>
+        <v>290.449008</v>
       </c>
       <c r="N81">
-        <v>-245.8183954</v>
+        <v>-249.449008</v>
       </c>
       <c r="O81">
-        <v>-54.08004698800001</v>
+        <v>-54.87878176000001</v>
       </c>
       <c r="P81">
-        <v>-191.7383484120001</v>
+        <v>-194.57022624</v>
       </c>
       <c r="Q81">
-        <v>-112.7383484120001</v>
+        <v>-115.57022624</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2389420800555422</v>
+        <v>0.2485991840583194</v>
       </c>
       <c r="T81">
-        <v>4.460556121375109</v>
+        <v>4.683583927443865</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03144847103485329</v>
+        <v>0.03105536514691763</v>
       </c>
       <c r="W81">
-        <v>0.2283844505299816</v>
+        <v>0.2284771448983568</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1429475956129695</v>
+        <v>0.1411607506678074</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2325015527303493</v>
+        <v>0.2344015527303493</v>
       </c>
       <c r="C82">
-        <v>-743.8840004020292</v>
+        <v>-763.4198448332118</v>
       </c>
       <c r="D82">
-        <v>478.9059995979711</v>
+        <v>474.7671551667884</v>
       </c>
       <c r="E82">
-        <v>739.2600000000002</v>
+        <v>754.6570000000002</v>
       </c>
       <c r="F82">
-        <v>1231.76</v>
+        <v>1247.157</v>
       </c>
       <c r="G82">
         <v>8.970000000000001</v>
@@ -8011,37 +8011,37 @@
         <v>41</v>
       </c>
       <c r="M82">
-        <v>290.449008</v>
+        <v>294.0796206000001</v>
       </c>
       <c r="N82">
-        <v>-249.449008</v>
+        <v>-253.0796206000001</v>
       </c>
       <c r="O82">
-        <v>-54.87878176000001</v>
+        <v>-55.67751653200001</v>
       </c>
       <c r="P82">
-        <v>-194.57022624</v>
+        <v>-197.402104068</v>
       </c>
       <c r="Q82">
-        <v>-115.57022624</v>
+        <v>-118.402104068</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2485991840583194</v>
+        <v>0.2592728253245467</v>
       </c>
       <c r="T82">
-        <v>4.683583927443865</v>
+        <v>4.930088344677753</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03105536514691763</v>
+        <v>0.03067196557720259</v>
       </c>
       <c r="W82">
-        <v>0.2284771448983568</v>
+        <v>0.2285675505168956</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1411607506678074</v>
+        <v>0.1394180253509208</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2344015527303493</v>
+        <v>0.2363015527303494</v>
       </c>
       <c r="C83">
-        <v>-763.4198448332118</v>
+        <v>-782.8847640348336</v>
       </c>
       <c r="D83">
-        <v>474.7671551667884</v>
+        <v>470.6992359651665</v>
       </c>
       <c r="E83">
-        <v>754.6570000000002</v>
+        <v>770.0540000000001</v>
       </c>
       <c r="F83">
-        <v>1247.157</v>
+        <v>1262.554</v>
       </c>
       <c r="G83">
         <v>8.970000000000001</v>
@@ -8093,37 +8093,37 @@
         <v>41</v>
       </c>
       <c r="M83">
-        <v>294.0796206000001</v>
+        <v>297.7102332</v>
       </c>
       <c r="N83">
-        <v>-253.0796206000001</v>
+        <v>-256.7102332</v>
       </c>
       <c r="O83">
-        <v>-55.67751653200001</v>
+        <v>-56.476251304</v>
       </c>
       <c r="P83">
-        <v>-197.402104068</v>
+        <v>-200.233981896</v>
       </c>
       <c r="Q83">
-        <v>-118.402104068</v>
+        <v>-121.233981896</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2592728253245467</v>
+        <v>0.2711324267314659</v>
       </c>
       <c r="T83">
-        <v>4.930088344677753</v>
+        <v>5.203982141604294</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03067196557720259</v>
+        <v>0.030297917216505</v>
       </c>
       <c r="W83">
-        <v>0.2285675505168956</v>
+        <v>0.2286557511203481</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1394180253509208</v>
+        <v>0.1377178055295682</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2363015527303494</v>
+        <v>0.2382015527303493</v>
       </c>
       <c r="C84">
-        <v>-782.8847640348336</v>
+        <v>-802.2805656320161</v>
       </c>
       <c r="D84">
-        <v>470.6992359651665</v>
+        <v>466.7004343679841</v>
       </c>
       <c r="E84">
-        <v>770.0540000000001</v>
+        <v>785.4510000000002</v>
       </c>
       <c r="F84">
-        <v>1262.554</v>
+        <v>1277.951</v>
       </c>
       <c r="G84">
         <v>8.970000000000001</v>
@@ -8175,37 +8175,37 @@
         <v>41</v>
       </c>
       <c r="M84">
-        <v>297.7102332</v>
+        <v>301.3408458000001</v>
       </c>
       <c r="N84">
-        <v>-256.7102332</v>
+        <v>-260.3408458000001</v>
       </c>
       <c r="O84">
-        <v>-56.476251304</v>
+        <v>-57.27498607600001</v>
       </c>
       <c r="P84">
-        <v>-200.233981896</v>
+        <v>-203.0658597240001</v>
       </c>
       <c r="Q84">
-        <v>-121.233981896</v>
+        <v>-124.0658597240001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2711324267314659</v>
+        <v>0.2843872753627287</v>
       </c>
       <c r="T84">
-        <v>5.203982141604294</v>
+        <v>5.510098738169254</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.030297917216505</v>
+        <v>0.02993288206931819</v>
       </c>
       <c r="W84">
-        <v>0.2286557511203481</v>
+        <v>0.2287418264080548</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1377178055295682</v>
+        <v>0.1360585548605372</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2382015527303493</v>
+        <v>0.2401015527303494</v>
       </c>
       <c r="C85">
-        <v>-802.2805656320161</v>
+        <v>-821.6089963409776</v>
       </c>
       <c r="D85">
-        <v>466.7004343679841</v>
+        <v>462.7690036590226</v>
       </c>
       <c r="E85">
-        <v>785.4510000000002</v>
+        <v>800.8480000000002</v>
       </c>
       <c r="F85">
-        <v>1277.951</v>
+        <v>1293.348</v>
       </c>
       <c r="G85">
         <v>8.970000000000001</v>
@@ -8257,37 +8257,37 @@
         <v>41</v>
       </c>
       <c r="M85">
-        <v>301.3408458000001</v>
+        <v>304.9714584000001</v>
       </c>
       <c r="N85">
-        <v>-260.3408458000001</v>
+        <v>-263.9714584000001</v>
       </c>
       <c r="O85">
-        <v>-57.27498607600001</v>
+        <v>-58.07372084800001</v>
       </c>
       <c r="P85">
-        <v>-203.0658597240001</v>
+        <v>-205.8977375520001</v>
       </c>
       <c r="Q85">
-        <v>-124.0658597240001</v>
+        <v>-126.8977375520001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2843872753627287</v>
+        <v>0.2992989800728993</v>
       </c>
       <c r="T85">
-        <v>5.510098738169254</v>
+        <v>5.854479909304834</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02993288206931819</v>
+        <v>0.02957653823515964</v>
       </c>
       <c r="W85">
-        <v>0.2287418264080548</v>
+        <v>0.2288258522841494</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1360585548605372</v>
+        <v>0.1344388101598165</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2401015527303493</v>
+        <v>0.2420015527303493</v>
       </c>
       <c r="C86">
-        <v>-821.6089963409775</v>
+        <v>-840.8717445130507</v>
       </c>
       <c r="D86">
-        <v>462.7690036590224</v>
+        <v>458.9032554869492</v>
       </c>
       <c r="E86">
-        <v>800.848</v>
+        <v>816.2449999999999</v>
       </c>
       <c r="F86">
-        <v>1293.348</v>
+        <v>1308.745</v>
       </c>
       <c r="G86">
         <v>8.970000000000001</v>
@@ -8339,37 +8339,37 @@
         <v>41</v>
       </c>
       <c r="M86">
-        <v>304.9714584</v>
+        <v>308.602071</v>
       </c>
       <c r="N86">
-        <v>-263.9714584</v>
+        <v>-267.602071</v>
       </c>
       <c r="O86">
-        <v>-58.073720848</v>
+        <v>-58.87245561999999</v>
       </c>
       <c r="P86">
-        <v>-205.897737552</v>
+        <v>-208.72961538</v>
       </c>
       <c r="Q86">
-        <v>-126.897737552</v>
+        <v>-129.72961538</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2992989800728991</v>
+        <v>0.3161989120777591</v>
       </c>
       <c r="T86">
-        <v>5.854479909304829</v>
+        <v>6.244778569925152</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02957653823515964</v>
+        <v>0.02922857896180483</v>
       </c>
       <c r="W86">
-        <v>0.2288258522841494</v>
+        <v>0.2289079010808064</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1344388101598166</v>
+        <v>0.1328571770991128</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2420015527303493</v>
+        <v>0.2439015527303493</v>
       </c>
       <c r="C87">
-        <v>-840.8717445130507</v>
+        <v>-860.0704425522472</v>
       </c>
       <c r="D87">
-        <v>458.9032554869492</v>
+        <v>455.1015574477528</v>
       </c>
       <c r="E87">
-        <v>816.2449999999999</v>
+        <v>831.6420000000001</v>
       </c>
       <c r="F87">
-        <v>1308.745</v>
+        <v>1324.142</v>
       </c>
       <c r="G87">
         <v>8.970000000000001</v>
@@ -8421,37 +8421,37 @@
         <v>41</v>
       </c>
       <c r="M87">
-        <v>308.602071</v>
+        <v>312.2326836</v>
       </c>
       <c r="N87">
-        <v>-267.602071</v>
+        <v>-271.2326836</v>
       </c>
       <c r="O87">
-        <v>-58.87245561999999</v>
+        <v>-59.67119039200001</v>
       </c>
       <c r="P87">
-        <v>-208.72961538</v>
+        <v>-211.561493208</v>
       </c>
       <c r="Q87">
-        <v>-129.72961538</v>
+        <v>-132.561493208</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3161989120777591</v>
+        <v>0.3355131200833133</v>
       </c>
       <c r="T87">
-        <v>6.244778569925152</v>
+        <v>6.690834182062663</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02922857896180483</v>
+        <v>0.02888871176457454</v>
       </c>
       <c r="W87">
-        <v>0.2289079010808064</v>
+        <v>0.2289880417659133</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1328571770991128</v>
+        <v>0.1313123262026116</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2439015527303493</v>
+        <v>0.2458015527303493</v>
       </c>
       <c r="C88">
-        <v>-860.0704425522472</v>
+        <v>-879.2066692136418</v>
       </c>
       <c r="D88">
-        <v>455.1015574477528</v>
+        <v>451.3623307863581</v>
       </c>
       <c r="E88">
-        <v>831.6420000000001</v>
+        <v>847.039</v>
       </c>
       <c r="F88">
-        <v>1324.142</v>
+        <v>1339.539</v>
       </c>
       <c r="G88">
         <v>8.970000000000001</v>
@@ -8503,37 +8503,37 @@
         <v>41</v>
       </c>
       <c r="M88">
-        <v>312.2326836</v>
+        <v>315.8632962</v>
       </c>
       <c r="N88">
-        <v>-271.2326836</v>
+        <v>-274.8632962</v>
       </c>
       <c r="O88">
-        <v>-59.67119039200001</v>
+        <v>-60.46992516400001</v>
       </c>
       <c r="P88">
-        <v>-211.561493208</v>
+        <v>-214.393371036</v>
       </c>
       <c r="Q88">
-        <v>-132.561493208</v>
+        <v>-135.393371036</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3355131200833133</v>
+        <v>0.3577987447051066</v>
       </c>
       <c r="T88">
-        <v>6.690834182062663</v>
+        <v>7.205513734529021</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02888871176457454</v>
+        <v>0.02855665760636103</v>
       </c>
       <c r="W88">
-        <v>0.2289880417659133</v>
+        <v>0.2290663401364201</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1313123262026116</v>
+        <v>0.1298029891198229</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2458015527303493</v>
+        <v>0.2477015527303493</v>
       </c>
       <c r="C89">
-        <v>-879.2066692136418</v>
+        <v>-898.2819517893778</v>
       </c>
       <c r="D89">
-        <v>451.3623307863581</v>
+        <v>447.6840482106223</v>
       </c>
       <c r="E89">
-        <v>847.039</v>
+        <v>862.4360000000001</v>
       </c>
       <c r="F89">
-        <v>1339.539</v>
+        <v>1354.936</v>
       </c>
       <c r="G89">
         <v>8.970000000000001</v>
@@ -8585,37 +8585,37 @@
         <v>41</v>
       </c>
       <c r="M89">
-        <v>315.8632962</v>
+        <v>319.4939088</v>
       </c>
       <c r="N89">
-        <v>-274.8632962</v>
+        <v>-278.4939088</v>
       </c>
       <c r="O89">
-        <v>-60.46992516400001</v>
+        <v>-61.26865993600001</v>
       </c>
       <c r="P89">
-        <v>-214.393371036</v>
+        <v>-217.225248864</v>
       </c>
       <c r="Q89">
-        <v>-135.393371036</v>
+        <v>-138.225248864</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3577987447051066</v>
+        <v>0.3837986400971989</v>
       </c>
       <c r="T89">
-        <v>7.205513734529021</v>
+        <v>7.805973212406442</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02855665760636103</v>
+        <v>0.02823215013356148</v>
       </c>
       <c r="W89">
-        <v>0.2290663401364201</v>
+        <v>0.2291428589985062</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1298029891198229</v>
+        <v>0.1283279551525521</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2477015527303493</v>
+        <v>0.2496015527303493</v>
       </c>
       <c r="C90">
-        <v>-898.2819517893778</v>
+        <v>-917.2977681886462</v>
       </c>
       <c r="D90">
-        <v>447.6840482106223</v>
+        <v>444.0652318113538</v>
       </c>
       <c r="E90">
-        <v>862.4360000000001</v>
+        <v>877.8330000000001</v>
       </c>
       <c r="F90">
-        <v>1354.936</v>
+        <v>1370.333</v>
       </c>
       <c r="G90">
         <v>8.970000000000001</v>
@@ -8667,37 +8667,37 @@
         <v>41</v>
       </c>
       <c r="M90">
-        <v>319.4939088</v>
+        <v>323.1245214</v>
       </c>
       <c r="N90">
-        <v>-278.4939088</v>
+        <v>-282.1245214</v>
       </c>
       <c r="O90">
-        <v>-61.26865993600001</v>
+        <v>-62.06739470800001</v>
       </c>
       <c r="P90">
-        <v>-217.225248864</v>
+        <v>-220.0571266920001</v>
       </c>
       <c r="Q90">
-        <v>-138.225248864</v>
+        <v>-141.0571266920001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3837986400971989</v>
+        <v>0.4145257891969443</v>
       </c>
       <c r="T90">
-        <v>7.805973212406442</v>
+        <v>8.515607140807028</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02823215013356148</v>
+        <v>0.02791493496352146</v>
       </c>
       <c r="W90">
-        <v>0.2291428589985062</v>
+        <v>0.2292176583356016</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1283279551525521</v>
+        <v>0.1268860680160067</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2496015527303493</v>
+        <v>0.2515015527303494</v>
       </c>
       <c r="C91">
-        <v>-917.2977681886462</v>
+        <v>-936.2555489175986</v>
       </c>
       <c r="D91">
-        <v>444.0652318113538</v>
+        <v>440.5044510824014</v>
       </c>
       <c r="E91">
-        <v>877.8330000000001</v>
+        <v>893.23</v>
       </c>
       <c r="F91">
-        <v>1370.333</v>
+        <v>1385.73</v>
       </c>
       <c r="G91">
         <v>8.970000000000001</v>
@@ -8749,37 +8749,37 @@
         <v>41</v>
       </c>
       <c r="M91">
-        <v>323.1245214</v>
+        <v>326.755134</v>
       </c>
       <c r="N91">
-        <v>-282.1245214</v>
+        <v>-285.755134</v>
       </c>
       <c r="O91">
-        <v>-62.06739470800001</v>
+        <v>-62.86612948</v>
       </c>
       <c r="P91">
-        <v>-220.0571266920001</v>
+        <v>-222.88900452</v>
       </c>
       <c r="Q91">
-        <v>-141.0571266920001</v>
+        <v>-143.88900452</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4145257891969443</v>
+        <v>0.4513983681166387</v>
       </c>
       <c r="T91">
-        <v>8.515607140807028</v>
+        <v>9.367167854887731</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02791493496352146</v>
+        <v>0.02760476901948234</v>
       </c>
       <c r="W91">
-        <v>0.2292176583356016</v>
+        <v>0.2292907954652061</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1268860680160067</v>
+        <v>0.1254762228158288</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2515015527303494</v>
+        <v>0.2534015527303493</v>
       </c>
       <c r="C92">
-        <v>-936.2555489175986</v>
+        <v>-955.1566789647566</v>
       </c>
       <c r="D92">
-        <v>440.5044510824014</v>
+        <v>437.0003210352436</v>
       </c>
       <c r="E92">
-        <v>893.23</v>
+        <v>908.6270000000002</v>
       </c>
       <c r="F92">
-        <v>1385.73</v>
+        <v>1401.127</v>
       </c>
       <c r="G92">
         <v>8.970000000000001</v>
@@ -8831,37 +8831,37 @@
         <v>41</v>
       </c>
       <c r="M92">
-        <v>326.755134</v>
+        <v>330.3857466000001</v>
       </c>
       <c r="N92">
-        <v>-285.755134</v>
+        <v>-289.3857466000001</v>
       </c>
       <c r="O92">
-        <v>-62.86612948</v>
+        <v>-63.66486425200002</v>
       </c>
       <c r="P92">
-        <v>-222.88900452</v>
+        <v>-225.720882348</v>
       </c>
       <c r="Q92">
-        <v>-143.88900452</v>
+        <v>-146.720882348</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4513983681166387</v>
+        <v>0.4964648534629319</v>
       </c>
       <c r="T92">
-        <v>9.367167854887731</v>
+        <v>10.40796428320859</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02760476901948234</v>
+        <v>0.02730141990937813</v>
       </c>
       <c r="W92">
-        <v>0.2292907954652061</v>
+        <v>0.2293623251853686</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1254762228158288</v>
+        <v>0.1240973632244461</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2534015527303493</v>
+        <v>0.2553015527303493</v>
       </c>
       <c r="C93">
-        <v>-955.1566789647566</v>
+        <v>-974.0024995971453</v>
       </c>
       <c r="D93">
-        <v>437.0003210352436</v>
+        <v>433.5515004028548</v>
       </c>
       <c r="E93">
-        <v>908.6270000000002</v>
+        <v>924.0240000000001</v>
       </c>
       <c r="F93">
-        <v>1401.127</v>
+        <v>1416.524</v>
       </c>
       <c r="G93">
         <v>8.970000000000001</v>
@@ -8913,37 +8913,37 @@
         <v>41</v>
       </c>
       <c r="M93">
-        <v>330.3857466000001</v>
+        <v>334.0163592000001</v>
       </c>
       <c r="N93">
-        <v>-289.3857466000001</v>
+        <v>-293.0163592000001</v>
       </c>
       <c r="O93">
-        <v>-63.66486425200002</v>
+        <v>-64.46359902400002</v>
       </c>
       <c r="P93">
-        <v>-225.720882348</v>
+        <v>-228.552760176</v>
       </c>
       <c r="Q93">
-        <v>-146.720882348</v>
+        <v>-149.552760176</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4964648534629319</v>
+        <v>0.5527979601457985</v>
       </c>
       <c r="T93">
-        <v>10.40796428320859</v>
+        <v>11.70895981860967</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02730141990937813</v>
+        <v>0.02700466534514576</v>
       </c>
       <c r="W93">
-        <v>0.2293623251853686</v>
+        <v>0.2294322999116146</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1240973632244461</v>
+        <v>0.1227484788415716</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2553015527303493</v>
+        <v>0.2572015527303493</v>
       </c>
       <c r="C94">
-        <v>-974.0024995971453</v>
+        <v>-992.7943100720418</v>
       </c>
       <c r="D94">
-        <v>433.5515004028548</v>
+        <v>430.1566899279583</v>
       </c>
       <c r="E94">
-        <v>924.0240000000001</v>
+        <v>939.421</v>
       </c>
       <c r="F94">
-        <v>1416.524</v>
+        <v>1431.921</v>
       </c>
       <c r="G94">
         <v>8.970000000000001</v>
@@ -8995,37 +8995,37 @@
         <v>41</v>
       </c>
       <c r="M94">
-        <v>334.0163592000001</v>
+        <v>337.6469718</v>
       </c>
       <c r="N94">
-        <v>-293.0163592000001</v>
+        <v>-296.6469718</v>
       </c>
       <c r="O94">
-        <v>-64.46359902400002</v>
+        <v>-65.26233379600001</v>
       </c>
       <c r="P94">
-        <v>-228.552760176</v>
+        <v>-231.384638004</v>
       </c>
       <c r="Q94">
-        <v>-149.552760176</v>
+        <v>-152.384638004</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5527979601457985</v>
+        <v>0.625226240166627</v>
       </c>
       <c r="T94">
-        <v>11.70895981860967</v>
+        <v>13.38166836412534</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02700466534514576</v>
+        <v>0.02671429259949903</v>
       </c>
       <c r="W94">
-        <v>0.2294322999116146</v>
+        <v>0.2295007698050381</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1227484788415716</v>
+        <v>0.1214286027249957</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2572015527303493</v>
+        <v>0.2591015527303493</v>
       </c>
       <c r="C95">
-        <v>-992.7943100720418</v>
+        <v>-1011.533369268927</v>
       </c>
       <c r="D95">
-        <v>430.1566899279583</v>
+        <v>426.8146307310728</v>
       </c>
       <c r="E95">
-        <v>939.421</v>
+        <v>954.8180000000002</v>
       </c>
       <c r="F95">
-        <v>1431.921</v>
+        <v>1447.318</v>
       </c>
       <c r="G95">
         <v>8.970000000000001</v>
@@ -9077,37 +9077,37 @@
         <v>41</v>
       </c>
       <c r="M95">
-        <v>337.6469718</v>
+        <v>341.2775844000001</v>
       </c>
       <c r="N95">
-        <v>-296.6469718</v>
+        <v>-300.2775844000001</v>
       </c>
       <c r="O95">
-        <v>-65.26233379600001</v>
+        <v>-66.06106856800002</v>
       </c>
       <c r="P95">
-        <v>-231.384638004</v>
+        <v>-234.2165158320001</v>
       </c>
       <c r="Q95">
-        <v>-152.384638004</v>
+        <v>-155.2165158320001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.625226240166627</v>
+        <v>0.7217972801943984</v>
       </c>
       <c r="T95">
-        <v>13.38166836412534</v>
+        <v>15.6119464248129</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02671429259949903</v>
+        <v>0.0264300979973767</v>
       </c>
       <c r="W95">
-        <v>0.2295007698050381</v>
+        <v>0.2295677828922186</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1214286027249957</v>
+        <v>0.1201368090789851</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2591015527303493</v>
+        <v>0.2610015527303494</v>
       </c>
       <c r="C96">
-        <v>-1011.533369268927</v>
+        <v>-1030.220897245951</v>
       </c>
       <c r="D96">
-        <v>426.8146307310728</v>
+        <v>423.5241027540489</v>
       </c>
       <c r="E96">
-        <v>954.8180000000002</v>
+        <v>970.2150000000001</v>
       </c>
       <c r="F96">
-        <v>1447.318</v>
+        <v>1462.715</v>
       </c>
       <c r="G96">
         <v>8.970000000000001</v>
@@ -9159,37 +9159,37 @@
         <v>41</v>
       </c>
       <c r="M96">
-        <v>341.2775844000001</v>
+        <v>344.908197</v>
       </c>
       <c r="N96">
-        <v>-300.2775844000001</v>
+        <v>-303.908197</v>
       </c>
       <c r="O96">
-        <v>-66.06106856800002</v>
+        <v>-66.85980334000001</v>
       </c>
       <c r="P96">
-        <v>-234.2165158320001</v>
+        <v>-237.04839366</v>
       </c>
       <c r="Q96">
-        <v>-155.2165158320001</v>
+        <v>-158.04839366</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7217972801943984</v>
+        <v>0.8569967362332783</v>
       </c>
       <c r="T96">
-        <v>15.6119464248129</v>
+        <v>18.73433570977548</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0264300979973767</v>
+        <v>0.02615188643950958</v>
       </c>
       <c r="W96">
-        <v>0.2295677828922186</v>
+        <v>0.2296333851775637</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1201368090789851</v>
+        <v>0.11887221108868</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2610015527303494</v>
+        <v>0.2629015527303493</v>
       </c>
       <c r="C97">
-        <v>-1030.220897245951</v>
+        <v>-1048.858076724946</v>
       </c>
       <c r="D97">
-        <v>423.5241027540489</v>
+        <v>420.2839232750536</v>
       </c>
       <c r="E97">
-        <v>970.2150000000001</v>
+        <v>985.6120000000001</v>
       </c>
       <c r="F97">
-        <v>1462.715</v>
+        <v>1478.112</v>
       </c>
       <c r="G97">
         <v>8.970000000000001</v>
@@ -9241,37 +9241,37 @@
         <v>41</v>
       </c>
       <c r="M97">
-        <v>344.908197</v>
+        <v>348.5388096</v>
       </c>
       <c r="N97">
-        <v>-303.908197</v>
+        <v>-307.5388096</v>
       </c>
       <c r="O97">
-        <v>-66.85980334000001</v>
+        <v>-67.658538112</v>
       </c>
       <c r="P97">
-        <v>-237.04839366</v>
+        <v>-239.880271488</v>
       </c>
       <c r="Q97">
-        <v>-158.04839366</v>
+        <v>-160.880271488</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8569967362332783</v>
+        <v>1.059795920291599</v>
       </c>
       <c r="T97">
-        <v>18.73433570977548</v>
+        <v>23.41791963721936</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02615188643950958</v>
+        <v>0.02587947095576469</v>
       </c>
       <c r="W97">
-        <v>0.2296333851775637</v>
+        <v>0.2296976207486307</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.11887221108868</v>
+        <v>0.1176339588898395</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2629015527303493</v>
+        <v>0.2648015527303493</v>
       </c>
       <c r="C98">
-        <v>-1048.858076724946</v>
+        <v>-1067.4460545088</v>
       </c>
       <c r="D98">
-        <v>420.2839232750536</v>
+        <v>417.0929454912006</v>
       </c>
       <c r="E98">
-        <v>985.6120000000001</v>
+        <v>1001.009</v>
       </c>
       <c r="F98">
-        <v>1478.112</v>
+        <v>1493.509</v>
       </c>
       <c r="G98">
         <v>8.970000000000001</v>
@@ -9323,37 +9323,37 @@
         <v>41</v>
       </c>
       <c r="M98">
-        <v>348.5388096</v>
+        <v>352.1694222</v>
       </c>
       <c r="N98">
-        <v>-307.5388096</v>
+        <v>-311.1694222</v>
       </c>
       <c r="O98">
-        <v>-67.658538112</v>
+        <v>-68.45727288400001</v>
       </c>
       <c r="P98">
-        <v>-239.880271488</v>
+        <v>-242.712149316</v>
       </c>
       <c r="Q98">
-        <v>-160.880271488</v>
+        <v>-163.712149316</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.059795920291596</v>
+        <v>1.397794560388794</v>
       </c>
       <c r="T98">
-        <v>23.4179196372193</v>
+        <v>31.22389284962574</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02587947095576469</v>
+        <v>0.02561267228611763</v>
       </c>
       <c r="W98">
-        <v>0.2296976207486307</v>
+        <v>0.2297605318749335</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1176339588898395</v>
+        <v>0.116421237664171</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2648015527303493</v>
+        <v>0.2667015527303493</v>
       </c>
       <c r="C99">
-        <v>-1067.4460545088</v>
+        <v>-1085.985942834734</v>
       </c>
       <c r="D99">
-        <v>417.0929454912006</v>
+        <v>413.9500571652664</v>
       </c>
       <c r="E99">
-        <v>1001.009</v>
+        <v>1016.406</v>
       </c>
       <c r="F99">
-        <v>1493.509</v>
+        <v>1508.906</v>
       </c>
       <c r="G99">
         <v>8.970000000000001</v>
@@ -9405,37 +9405,37 @@
         <v>41</v>
       </c>
       <c r="M99">
-        <v>352.1694222</v>
+        <v>355.8000348</v>
       </c>
       <c r="N99">
-        <v>-311.1694222</v>
+        <v>-314.8000348</v>
       </c>
       <c r="O99">
-        <v>-68.45727288400001</v>
+        <v>-69.25600765599999</v>
       </c>
       <c r="P99">
-        <v>-242.712149316</v>
+        <v>-245.544027144</v>
       </c>
       <c r="Q99">
-        <v>-163.712149316</v>
+        <v>-166.544027144</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.397794560388794</v>
+        <v>2.073791840583191</v>
       </c>
       <c r="T99">
-        <v>31.22389284962574</v>
+        <v>46.83583927443861</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02561267228611763</v>
+        <v>0.0253513184872797</v>
       </c>
       <c r="W99">
-        <v>0.2297605318749335</v>
+        <v>0.2298221591006995</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.116421237664171</v>
+        <v>0.1152332658512714</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2667015527303493</v>
+        <v>0.2686015527303493</v>
       </c>
       <c r="C100">
-        <v>-1085.985942834734</v>
+        <v>-1104.478820666872</v>
       </c>
       <c r="D100">
-        <v>413.9500571652664</v>
+        <v>410.8541793331285</v>
       </c>
       <c r="E100">
-        <v>1016.406</v>
+        <v>1031.803</v>
       </c>
       <c r="F100">
-        <v>1508.906</v>
+        <v>1524.303</v>
       </c>
       <c r="G100">
         <v>8.970000000000001</v>
@@ -9487,37 +9487,37 @@
         <v>41</v>
       </c>
       <c r="M100">
-        <v>355.8000348</v>
+        <v>359.4306474000001</v>
       </c>
       <c r="N100">
-        <v>-314.8000348</v>
+        <v>-318.4306474000001</v>
       </c>
       <c r="O100">
-        <v>-69.25600765599999</v>
+        <v>-70.05474242800001</v>
       </c>
       <c r="P100">
-        <v>-245.544027144</v>
+        <v>-248.3759049720001</v>
       </c>
       <c r="Q100">
-        <v>-166.544027144</v>
+        <v>-169.3759049720001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.073791840583191</v>
+        <v>4.101783681166383</v>
       </c>
       <c r="T100">
-        <v>46.83583927443861</v>
+        <v>93.67167854887721</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0253513184872797</v>
+        <v>0.02509524456316576</v>
       </c>
       <c r="W100">
-        <v>0.2298221591006995</v>
+        <v>0.2298825413320055</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1152332658512714</v>
+        <v>0.1140692934689352</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2686015527303493</v>
-      </c>
-      <c r="C101">
-        <v>-1104.478820666872</v>
-      </c>
-      <c r="D101">
-        <v>410.8541793331285</v>
-      </c>
-      <c r="E101">
-        <v>1031.803</v>
-      </c>
-      <c r="F101">
-        <v>1524.303</v>
-      </c>
-      <c r="G101">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="H101">
-        <v>1047.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>120</v>
-      </c>
-      <c r="K101">
-        <v>79</v>
-      </c>
-      <c r="L101">
-        <v>41</v>
-      </c>
-      <c r="M101">
-        <v>359.4306474000001</v>
-      </c>
-      <c r="N101">
-        <v>-318.4306474000001</v>
-      </c>
-      <c r="O101">
-        <v>-70.05474242800001</v>
-      </c>
-      <c r="P101">
-        <v>-248.3759049720001</v>
-      </c>
-      <c r="Q101">
-        <v>-169.3759049720001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.101783681166383</v>
-      </c>
-      <c r="T101">
-        <v>93.67167854887721</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02509524456316576</v>
-      </c>
-      <c r="W101">
-        <v>0.2298825413320055</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1140692934689352</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
